--- a/files/九龙-旺角-利奥坊．凯岸.xlsx
+++ b/files/九龙-旺角-利奥坊．凯岸.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -752,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -798,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -839,7 +702,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -894,7 +757,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -940,7 +803,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -986,7 +849,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1032,7 +895,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1078,7 +941,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1124,7 +987,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1170,7 +1033,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1216,7 +1079,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1262,7 +1125,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1308,7 +1171,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-08</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1354,7 +1217,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1400,7 +1263,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1446,7 +1309,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1492,7 +1355,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1538,7 +1401,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1584,7 +1447,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1630,7 +1493,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1722,7 +1585,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1768,7 +1631,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1814,7 +1677,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1860,7 +1723,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1952,7 +1815,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1998,7 +1861,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2044,7 +1907,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2090,7 +1953,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2136,7 +1999,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2182,7 +2045,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2274,7 +2137,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2320,7 +2183,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2366,7 +2229,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2412,7 +2275,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2458,7 +2321,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2504,7 +2367,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2550,7 +2413,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2596,7 +2459,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2642,7 +2505,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2688,7 +2551,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2734,7 +2597,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2780,7 +2643,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2826,7 +2689,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2872,7 +2735,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2918,7 +2781,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-22</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2964,7 +2827,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3010,7 +2873,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3102,7 +2965,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3148,7 +3011,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3194,7 +3057,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3286,7 +3149,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3332,7 +3195,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3378,7 +3241,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3424,7 +3287,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3470,7 +3333,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3516,7 +3379,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3562,7 +3425,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3608,7 +3471,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3654,7 +3517,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3700,7 +3563,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3746,7 +3609,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3792,7 +3655,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3838,7 +3701,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3884,7 +3747,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-25</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3930,7 +3793,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3976,7 +3839,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4022,7 +3885,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4068,7 +3931,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4114,7 +3977,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4206,7 +4069,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-21</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4252,7 +4115,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4298,7 +4161,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4344,7 +4207,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4390,7 +4253,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-25</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4436,7 +4299,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4482,7 +4345,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4528,7 +4391,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4574,7 +4437,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4620,7 +4483,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4666,7 +4529,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4712,7 +4575,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4758,7 +4621,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4804,7 +4667,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4850,7 +4713,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4896,7 +4759,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4942,7 +4805,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4988,7 +4851,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5034,7 +4897,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5080,7 +4943,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5172,7 +5035,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5218,7 +5081,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-05</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5264,7 +5127,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-08-15</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5310,7 +5173,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5356,7 +5219,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5402,7 +5265,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5448,7 +5311,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5494,7 +5357,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5540,7 +5403,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5632,7 +5495,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5678,7 +5541,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5724,7 +5587,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5770,7 +5633,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5816,7 +5679,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5862,7 +5725,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5908,7 +5771,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5954,7 +5817,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6000,7 +5863,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6092,7 +5955,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6138,7 +6001,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6184,7 +6047,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6276,7 +6139,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6322,7 +6185,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6368,7 +6231,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6414,7 +6277,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-15</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6460,7 +6323,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6506,7 +6369,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6552,7 +6415,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6598,7 +6461,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6644,7 +6507,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6690,7 +6553,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6736,7 +6599,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6782,7 +6645,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-27</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6828,7 +6691,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6874,7 +6737,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6920,7 +6783,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6966,7 +6829,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7012,7 +6875,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7058,7 +6921,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7104,7 +6967,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7150,7 +7013,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7196,7 +7059,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7242,7 +7105,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7288,7 +7151,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7334,7 +7197,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7380,7 +7243,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7426,7 +7289,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7518,7 +7381,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7564,7 +7427,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7610,7 +7473,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7656,7 +7519,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7702,7 +7565,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7748,7 +7611,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7794,7 +7657,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7840,7 +7703,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7886,7 +7749,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7932,7 +7795,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7978,7 +7841,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8024,7 +7887,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8070,7 +7933,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8116,7 +7979,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8162,7 +8025,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8208,7 +8071,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8254,7 +8117,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8300,7 +8163,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8346,7 +8209,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8392,7 +8255,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8438,7 +8301,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8484,7 +8347,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8530,7 +8393,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8576,7 +8439,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8622,7 +8485,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8714,7 +8577,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8760,7 +8623,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8806,7 +8669,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -8852,7 +8715,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8898,7 +8761,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -8944,7 +8807,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -8990,7 +8853,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9036,7 +8899,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9082,7 +8945,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9128,7 +8991,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9174,7 +9037,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9220,7 +9083,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9266,7 +9129,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9312,7 +9175,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9358,7 +9221,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9404,7 +9267,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9450,7 +9313,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9496,7 +9359,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9542,7 +9405,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9588,7 +9451,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9634,7 +9497,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9680,7 +9543,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9726,7 +9589,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9772,7 +9635,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9818,7 +9681,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-15</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9864,7 +9727,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9956,7 +9819,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10002,7 +9865,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10048,7 +9911,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10140,7 +10003,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10186,7 +10049,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10232,7 +10095,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10278,7 +10141,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10324,7 +10187,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10370,7 +10233,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10416,7 +10279,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10462,7 +10325,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10508,7 +10371,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10554,7 +10417,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-15</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10600,7 +10463,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10692,7 +10555,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10738,7 +10601,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10784,7 +10647,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10830,7 +10693,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10876,7 +10739,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10968,7 +10831,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11014,7 +10877,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-23</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11060,7 +10923,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11106,7 +10969,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11152,7 +11015,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11198,7 +11061,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11290,7 +11153,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11336,7 +11199,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11428,7 +11291,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11474,7 +11337,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11520,7 +11383,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11566,7 +11429,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11612,7 +11475,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11658,7 +11521,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11704,7 +11567,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11750,7 +11613,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11796,7 +11659,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11842,7 +11705,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11888,7 +11751,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -11934,7 +11797,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -11980,7 +11843,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-11</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12026,7 +11889,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12072,7 +11935,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12118,7 +11981,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12164,7 +12027,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12210,7 +12073,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12256,7 +12119,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12302,7 +12165,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12348,7 +12211,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12394,7 +12257,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12440,7 +12303,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12486,7 +12349,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12532,7 +12395,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-30</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12628,7 +12491,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12674,7 +12537,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12720,7 +12583,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12766,7 +12629,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-25</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12812,7 +12675,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -12858,7 +12721,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -12904,7 +12767,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -12950,7 +12813,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -12996,7 +12859,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13042,7 +12905,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-05</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13088,7 +12951,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13134,7 +12997,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13180,7 +13043,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13226,7 +13089,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13272,7 +13135,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -13318,7 +13181,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -13364,7 +13227,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13410,7 +13273,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13456,7 +13319,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-03</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13502,7 +13365,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13548,7 +13411,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13594,7 +13457,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13640,7 +13503,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-12</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13686,7 +13549,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13732,7 +13595,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -13778,7 +13641,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -13824,7 +13687,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13870,7 +13733,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13916,7 +13779,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -13962,7 +13825,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14008,7 +13871,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14054,7 +13917,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14100,7 +13963,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14146,7 +14009,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-24</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14192,7 +14055,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14284,7 +14147,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14330,7 +14193,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14422,7 +14285,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14468,7 +14331,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14514,7 +14377,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14606,7 +14469,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14652,7 +14515,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -14744,7 +14607,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -14790,7 +14653,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -14836,7 +14699,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14882,7 +14745,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -14928,7 +14791,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -14974,7 +14837,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15020,7 +14883,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-21</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15066,7 +14929,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15158,7 +15021,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -15204,7 +15067,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -15250,7 +15113,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -15296,7 +15159,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-26</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15342,7 +15205,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15388,7 +15251,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15434,7 +15297,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -15480,7 +15343,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -15526,7 +15389,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -15572,7 +15435,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15618,7 +15481,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15664,7 +15527,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -15710,7 +15573,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -15756,7 +15619,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -15802,7 +15665,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -15848,7 +15711,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -15894,7 +15757,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -15940,7 +15803,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -15986,7 +15849,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -16032,7 +15895,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -16078,7 +15941,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -16124,7 +15987,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16170,7 +16033,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -16216,7 +16079,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16262,7 +16125,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -16308,7 +16171,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -16354,7 +16217,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -16400,7 +16263,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -16446,7 +16309,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -16492,7 +16355,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16584,7 +16447,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -16630,7 +16493,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16676,7 +16539,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -16722,7 +16585,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -16768,7 +16631,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -16814,7 +16677,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -16860,7 +16723,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -16906,7 +16769,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -16952,7 +16815,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -16998,7 +16861,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17044,7 +16907,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-20</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17090,7 +16953,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -17136,7 +16999,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -17182,7 +17045,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17228,7 +17091,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17274,7 +17137,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -17320,7 +17183,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -17366,7 +17229,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -17458,7 +17321,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -17504,7 +17367,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -17596,7 +17459,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -17642,7 +17505,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -17688,7 +17551,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -17734,7 +17597,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -17780,7 +17643,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -17826,7 +17689,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -17872,7 +17735,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -17918,7 +17781,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -17964,7 +17827,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -18010,7 +17873,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -18056,7 +17919,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -18102,7 +17965,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -18148,7 +18011,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -18194,7 +18057,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -18240,7 +18103,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -18286,7 +18149,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-11</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -18332,7 +18195,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -18378,7 +18241,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -18424,7 +18287,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -18516,7 +18379,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -18562,7 +18425,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -18608,7 +18471,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -18654,7 +18517,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -18700,7 +18563,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -18746,7 +18609,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -18792,7 +18655,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -18838,7 +18701,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -18884,7 +18747,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -18930,7 +18793,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -18976,7 +18839,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -19068,7 +18931,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -19114,7 +18977,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -19160,7 +19023,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -19206,7 +19069,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -19252,7 +19115,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -19298,7 +19161,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -19344,7 +19207,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -19390,7 +19253,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -19436,7 +19299,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -19482,7 +19345,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -19528,7 +19391,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -19620,7 +19483,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -19666,7 +19529,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -19758,7 +19621,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -19804,7 +19667,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -19850,7 +19713,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -19896,7 +19759,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -19942,7 +19805,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -19988,7 +19851,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -20034,7 +19897,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -20080,7 +19943,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -20126,7 +19989,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -20172,7 +20035,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -20218,7 +20081,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -20310,7 +20173,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -20356,7 +20219,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -20402,7 +20265,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -20448,7 +20311,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -20540,7 +20403,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -20586,7 +20449,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -20632,7 +20495,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -20678,7 +20541,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -20724,7 +20587,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -20770,7 +20633,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -20862,7 +20725,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -20908,7 +20771,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -21000,7 +20863,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -21046,7 +20909,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -21092,7 +20955,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -21138,7 +21001,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -21184,7 +21047,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -21230,7 +21093,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -21276,7 +21139,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -21368,7 +21231,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-21</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -21414,7 +21277,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -21460,7 +21323,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -21506,7 +21369,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -21552,7 +21415,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -21598,7 +21461,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -21644,7 +21507,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -21690,7 +21553,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -21736,7 +21599,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -21782,7 +21645,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -21828,7 +21691,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -21874,7 +21737,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -21920,7 +21783,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -21966,7 +21829,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -22012,7 +21875,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -22058,7 +21921,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -22104,7 +21967,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -22150,7 +22013,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -22196,7 +22059,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -22242,7 +22105,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -22288,7 +22151,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -22334,7 +22197,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -22380,7 +22243,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -22426,7 +22289,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -22518,7 +22381,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -22564,7 +22427,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -22610,7 +22473,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-27</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -22702,7 +22565,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -22748,7 +22611,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -22794,7 +22657,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-25</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -22840,7 +22703,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-17</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -22886,7 +22749,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -22932,7 +22795,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -22978,7 +22841,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -23024,7 +22887,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -23070,7 +22933,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -23116,7 +22979,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -23162,7 +23025,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -23208,7 +23071,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -23254,7 +23117,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-24</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -23346,7 +23209,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -23392,7 +23255,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -23438,7 +23301,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -23484,7 +23347,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -23576,7 +23439,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -23668,7 +23531,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-28</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -23714,7 +23577,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -23760,7 +23623,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -23806,7 +23669,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-09</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -23852,7 +23715,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -23898,7 +23761,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-20</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -23990,7 +23853,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -24036,7 +23899,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -24082,7 +23945,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -24128,7 +23991,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -24174,7 +24037,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -24220,7 +24083,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -24266,7 +24129,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -24312,7 +24175,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-03</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -24334,4796 +24197,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>利奥坊．凯岸 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>257 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>256 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 632呎 (3房)
-招标单位
--
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 508呎 (3房)
-$1,708万
-$33,622/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 509呎 (3房)
-$1,300万
-$25,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 579呎 (3房)
-$1,388万
-$23,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,079万
-$25,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$736万
-$29,341/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$746万
-$29,589/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$638万
-$32,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$801万
-$25,934/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$705万
-$27,861/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$448万
-$23,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$698万
-$28,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$693万
-$27,849/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$576万
-$20,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$605万
-$31,332/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$986万
-$23,646/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$727万
-$28,983/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$745万
-$29,557/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$637万
-$32,181/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$899万
-$29,091/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$696万
-$27,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$485万
-$25,019/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$696万
-$27,969/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$692万
-$27,801/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$569万
-$20,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$597万
-$30,936/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,173万
-$28,122/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$722万
-$28,773/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$724万
-$28,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$643万
-$32,475/呎
-(18年-08月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$863万
-$27,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$704万
-$27,832/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$535万
-$27,589/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$685万
-$27,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$653万
-$26,334/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$546万
-$19,630/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$620万
-$32,118/呎
-(18年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,157万
-$27,755/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$713万
-$28,398/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$730万
-$28,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$597万
-$30,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$861万
-$27,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$714万
-$28,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$537万
-$27,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$653万
-$26,236/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$649万
-$26,051/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$533万
-$19,186/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$616万
-$31,904/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,154万
-$27,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$703万
-$28,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$705万
-$27,995/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$595万
-$30,058/呎
-(21年-10月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$849万
-$27,491/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$688万
-$27,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$534万
-$27,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$642万
-$25,787/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$638万
-$25,604/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$530万
-$19,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$612万
-$31,695/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,161万
-$27,835/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$687万
-$27,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$711万
-$28,207/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$587万
-$29,653/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$829万
-$26,831/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$691万
-$27,297/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$525万
-$27,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$638万
-$25,612/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$633万
-$25,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$526万
-$18,929/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$601万
-$31,153/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,165万
-$27,934/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$689万
-$27,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$691万
-$27,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$493万
-$24,920/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$725万
-$23,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$679万
-$26,837/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$521万
-$26,879/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$653万
-$26,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$629万
-$25,257/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$617万
-$22,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$597万
-$30,946/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,123万
-$26,935/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$684万
-$27,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$687万
-$27,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$611万
-$30,861/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$818万
-$26,467/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$682万
-$26,941/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$518万
-$26,698/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$629万
-$25,268/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$631万
-$25,349/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$613万
-$22,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$576万
-$29,839/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,116万
-$26,751/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$694万
-$27,643/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$689万
-$27,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$607万
-$30,642/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$866万
-$28,042/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$677万
-$26,762/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$515万
-$26,522/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$631万
-$25,357/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$620万
-$24,910/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$600万
-$21,588/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$589万
-$30,518/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,108万
-$26,565/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$675万
-$26,891/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$692万
-$27,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$427万
-$21,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$835万
-$27,038/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$687万
-$27,142/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$516万
-$26,618/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$1,751万
-$70,317/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$622万
-$24,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$663万
-$23,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$586万
-$30,355/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,100万
-$26,380/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$670万
-$26,708/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$680万
-$26,979/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$455万
-$22,980/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$821万
-$26,398/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$661万
-$26,131/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$508万
-$26,184/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 248呎 (1房)
-$636万
-$25,630/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$612万
-$24,563/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$642万
-$23,094/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$570万
-$29,531/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,092万
-$26,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$666万
-$26,517/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$675万
-$26,796/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$588万
-$29,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$815万
-$26,218/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$677万
-$26,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$504万
-$25,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$631万
-$25,346/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$614万
-$24,648/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$638万
-$22,934/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$566万
-$29,327/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,085万
-$26,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$663万
-$26,425/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$673万
-$26,697/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 197呎 (开放式)
-$586万
-$29,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$818万
-$26,476/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$661万
-$26,140/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$502万
-$25,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$616万
-$24,744/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$605万
-$24,303/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$635万
-$22,853/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$562万
-$29,118/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,069万
-$25,639/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$658万
-$26,234/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$668万
-$26,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$447万
-$22,574/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$806万
-$25,929/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$657万
-$25,966/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$504万
-$25,989/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$612万
-$24,567/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$620万
-$24,994/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$639万
-$22,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$544万
-$28,205/呎
-(18年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,663万
-$39,889/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$654万
-$26,046/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$656万
-$26,050/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$438万
-$22,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$795万
-$25,559/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$680万
-$26,858/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$495万
-$25,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$607万
-$24,393/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$596万
-$23,952/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$626万
-$22,532/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$538万
-$27,885/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,035万
-$24,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$649万
-$25,863/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$665万
-$26,406/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$573万
-$28,956/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$789万
-$25,371/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$648万
-$25,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$492万
-$25,361/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$645万
-$25,890/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$598万
-$24,031/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$630万
-$22,659/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$534万
-$27,681/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,028万
-$24,641/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$644万
-$25,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$654万
-$25,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 197呎 (开放式)
-$575万
-$29,195/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$783万
-$25,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$637万
-$25,166/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$489万
-$25,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$592万
-$23,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$588万
-$23,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$726万
-$26,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$525万
-$27,186/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,031万
-$24,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$652万
-$25,975/呎
-(19年-07月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$663万
-$26,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$533万
-$26,897/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$769万
-$24,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$639万
-$25,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$511万
-$26,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$594万
-$23,869/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$584万
-$23,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$720万
-$25,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$521万
-$26,984/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,023万
-$24,529/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$635万
-$25,297/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$644万
-$25,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$529万
-$26,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$772万
-$24,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$641万
-$25,335/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$492万
-$25,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$590万
-$23,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$579万
-$23,258/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$708万
-$25,455/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$517万
-$26,777/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,008万
-$24,183/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$646万
-$25,726/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$635万
-$25,216/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 197呎 (开放式)
-$532万
-$27,016/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$785万
-$25,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$632万
-$24,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$485万
-$25,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$582万
-$23,361/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$583万
-$23,512/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$713万
-$25,630/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$515万
-$26,674/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$762万
-$18,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$628万
-$25,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$637万
-$25,291/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$528万
-$26,681/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (1房)
-$763万
-$24,534/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$621万
-$24,546/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$482万
-$24,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 248呎 (1房)
-$583万
-$23,524/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$573万
-$23,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$707万
-$25,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$553万
-$28,661/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,129万
-$27,085/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$621万
-$24,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$630万
-$25,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$522万
-$26,376/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 309呎 (1房)
-$754万
-$24,410/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$621万
-$24,539/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$476万
-$24,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$645万
-$25,897/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$566万
-$22,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$699万
-$25,157/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$499万
-$25,847/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 379呎 (2房)
-$788万
-$20,792/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 229呎 (1房)
-$721万
-$31,480/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 230呎 (1房)
-$740万
-$32,167/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 175呎 (开放式)
-$480万
-$27,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 290呎 (1房)
-$680万
-$23,448/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 233呎 (1房)
-$610万
-$26,180/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 171呎 (开放式)
-$596万
-$34,837/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 227呎 (1房)
-$681万
-$30,005/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 227呎 (1房)
-$693万
-$30,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 257呎 (1房)
-$635万
-$24,708/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 171呎 (开放式)
-$618万
-$36,123/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>利奥坊．凯岸 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>257 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>256 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 632呎 (3房)
-$2,000万
-$31,646/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 506呎 (3房)
-$1,689万
-$33,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>C | 509呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 579呎 (3房)
-$1,660万
-$28,670/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="18" t="inlineStr"/>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$951万
-$22,803/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$740万
-$29,496/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$739万
-$29,341/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$637万
-$32,160/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$766万
-$24,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$702万
-$27,747/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$550万
-$28,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$708万
-$28,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$751万
-$30,144/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$776万
-$27,926/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$383万
-$19,835/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,233万
-$29,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$724万
-$28,829/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$738万
-$29,291/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$629万
-$31,758/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$885万
-$28,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$701万
-$27,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$543万
-$27,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$707万
-$28,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$726万
-$29,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$767万
-$27,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$425万
-$22,002/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,127万
-$27,034/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$695万
-$27,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$709万
-$28,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$597万
-$30,141/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$848万
-$27,633/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$647万
-$25,556/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$517万
-$26,637/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$618万
-$24,817/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$647万
-$26,003/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$784万
-$28,203/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$527万
-$27,319/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,134万
-$27,199/呎
-(18年-07月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$660万
-$26,298/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$660万
-$26,179/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$589万
-$29,738/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$884万
-$28,782/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$642万
-$25,395/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$498万
-$25,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$614万
-$24,655/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$630万
-$25,307/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$643万
-$23,131/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$524万
-$27,141/呎
-(18年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,098万
-$26,334/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$645万
-$25,687/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$644万
-$25,575/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$553万
-$27,947/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$881万
-$28,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$645万
-$25,495/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$500万
-$25,762/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$610万
-$24,493/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$619万
-$24,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$766万
-$27,543/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$526万
-$27,248/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,072万
-$25,716/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$650万
-$25,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$643万
-$25,505/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$546万
-$27,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$869万
-$28,217/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$634万
-$25,068/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$491万
-$25,327/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$600万
-$24,078/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$615万
-$24,708/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$761万
-$27,362/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$517万
-$26,792/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,065万
-$25,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$625万
-$24,920/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$632万
-$25,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 197呎 (开放式)
-$542万
-$27,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$881万
-$28,608/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$637万
-$25,169/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$488万
-$25,160/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$596万
-$23,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$618万
-$24,802/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$727万
-$26,151/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$514万
-$26,615/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,069万
-$25,635/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$621万
-$24,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$628万
-$24,907/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$538万
-$27,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$866万
-$28,124/呎
-(18年-07月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$633万
-$25,006/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$485万
-$24,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$592万
-$23,758/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$607万
-$24,376/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$715万
-$25,705/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$516万
-$26,716/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,051万
-$25,194/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$617万
-$24,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$630万
-$25,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 197呎 (开放式)
-$529万
-$26,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$869万
-$28,305/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$622万
-$24,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$507万
-$26,139/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 248呎 (1房)
-$594万
-$23,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$622万
-$24,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$710万
-$25,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$507万
-$26,260/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$994万
-$23,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$619万
-$24,673/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$626万
-$24,830/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$525万
-$26,533/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$812万
-$26,366/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$624万
-$24,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$484万
-$24,925/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$584万
-$23,437/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$599万
-$24,141/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$712万
-$25,620/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$503万
-$26,083/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$977万
-$23,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$609万
-$24,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$694万
-$27,543/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$538万
-$27,178/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$815万
-$26,542/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$620万
-$24,512/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$490万
-$25,278/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$580万
-$23,273/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$601万
-$24,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$667万
-$23,983/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$500万
-$25,911/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$1,001万
-$23,995/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$611万
-$24,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$611万
-$24,240/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$523万
-$26,434/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$809万
-$26,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$610万
-$24,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$472万
-$24,338/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$576万
-$23,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$590万
-$23,712/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$662万
-$23,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$502万
-$26,005/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$973万
-$23,339/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$639万
-$25,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$615万
-$24,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$521万
-$26,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$795万
-$25,807/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$608万
-$24,013/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$475万
-$24,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$580万
-$23,275/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$588万
-$23,628/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$660万
-$23,731/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$498万
-$25,825/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$953万
-$22,852/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$652万
-$25,988/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$611万
-$24,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$518万
-$26,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$794万
-$25,795/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$610万
-$24,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$482万
-$24,849/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$570万
-$22,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$582万
-$23,474/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$650万
-$23,396/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$505万
-$26,181/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$953万
-$22,847/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$626万
-$24,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$607万
-$24,072/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$509万
-$25,688/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$741万
-$24,050/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$599万
-$23,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$479万
-$24,682/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$566万
-$22,712/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$576万
-$23,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$641万
-$23,061/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$486万
-$25,202/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$936万
-$22,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$603万
-$24,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$594万
-$23,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$508万
-$25,678/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 307呎 (1房)
-$735万
-$23,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$595万
-$23,528/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$461万
-$23,760/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$562万
-$22,552/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$590万
-$23,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$636万
-$22,895/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$483万
-$25,030/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$929万
-$22,281/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$599万
-$23,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$588万
-$23,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$498万
-$25,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$722万
-$23,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$591万
-$23,367/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$458万
-$23,593/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$558万
-$22,392/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$574万
-$23,036/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$625万
-$22,492/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$490万
-$25,376/呎
-(18年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$932万
-$22,352/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$594万
-$23,682/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$590万
-$23,402/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$494万
-$24,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$717万
-$23,275/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$587万
-$23,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$455万
-$23,432/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 248呎 (1房)
-$559万
-$22,556/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$564万
-$22,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$621万
-$22,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$469万
-$24,326/呎
-(18年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$925万
-$22,186/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$596万
-$23,759/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$585万
-$23,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$495万
-$25,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$719万
-$23,342/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$583万
-$23,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$456万
-$23,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$550万
-$22,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$565万
-$22,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$636万
-$22,861/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$459万
-$23,794/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$941万
-$22,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$594万
-$23,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$595万
-$23,629/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$488万
-$24,657/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$709万
-$23,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$581万
-$22,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$450万
-$23,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 248呎 (1房)
-$548万
-$22,080/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$575万
-$23,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$620万
-$22,308/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$458万
-$23,706/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$911万
-$21,857/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$584万
-$23,254/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$573万
-$22,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$490万
-$24,727/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$711万
-$23,077/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$577万
-$22,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$446万
-$23,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$588万
-$23,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 249呎 (1房)
-$553万
-$22,216/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$646万
-$23,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$496万
-$25,716/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 417呎 (2房)
-$920万
-$22,061/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 251呎 (1房)
-$595万
-$23,719/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 252呎 (1房)
-$567万
-$22,491/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 198呎 (开放式)
-$479万
-$24,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
-$717万
-$23,285/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 253呎 (1房)
-$578万
-$22,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 194呎 (开放式)
-$442万
-$22,771/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 249呎 (1房)
-$587万
-$23,591/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 248呎 (1房)
-$548万
-$22,091/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 278呎 (1房)
-$646万
-$23,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 193呎 (开放式)
-$491万
-$25,428/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 379呎 (2房)
-$1,170万
-$30,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 230呎 (1房)
-$700万
-$30,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 230呎 (1房)
-$721万
-$31,359/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 175呎 (开放式)
-$398万
-$22,743/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 286呎 (1房)
-$700万
-$24,476/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 233呎 (1房)
-$628万
-$26,953/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 171呎 (开放式)
-$450万
-$26,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 227呎 (1房)
-$693万
-$30,521/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 227呎 (1房)
-$716万
-$31,522/呎
-(18年-08月)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 257呎 (1房)
-$720万
-$28,016/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 171呎 (开放式)
-$380万
-$22,222/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-旺角-利奥坊．凯岸.xlsx
+++ b/files/九龙-旺角-利奥坊．凯岸.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -24197,4 +24377,4796 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 632呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 508呎 (3房)
+$1708万
+$33,622/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 509呎 (3房)
+$1300万
+$25,540/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 579呎 (3房)
+$1388万
+$23,972/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1079万
+$25,877/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$736万
+$29,341/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$746万
+$29,589/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$638万
+$32,227/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$801万
+$25,934/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$705万
+$27,861/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$448万
+$23,088/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$698万
+$28,012/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$693万
+$27,849/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$576万
+$20,730/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$605万
+$31,332/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$986万
+$23,646/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$727万
+$28,983/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$745万
+$29,557/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$637万
+$32,181/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$899万
+$29,091/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$696万
+$27,523/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$485万
+$25,019/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$696万
+$27,969/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$692万
+$27,801/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$569万
+$20,471/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$597万
+$30,936/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1173万
+$28,122/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$722万
+$28,773/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$724万
+$28,738/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$643万
+$32,475/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$863万
+$27,915/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$704万
+$27,832/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$535万
+$27,589/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$685万
+$27,510/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$653万
+$26,334/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$546万
+$19,630/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$620万
+$32,118/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1157万
+$27,755/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$713万
+$28,398/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$730万
+$28,961/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$597万
+$30,127/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$861万
+$27,860/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$714万
+$28,230/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$537万
+$27,701/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$653万
+$26,236/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$649万
+$26,051/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$533万
+$19,186/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$616万
+$31,904/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1154万
+$27,679/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$703万
+$28,024/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$705万
+$27,995/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$595万
+$30,058/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$849万
+$27,491/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$688万
+$27,193/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$534万
+$27,523/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$642万
+$25,787/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$638万
+$25,604/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$530万
+$19,059/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$612万
+$31,695/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1161万
+$27,835/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$687万
+$27,357/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$711万
+$28,207/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$587万
+$29,653/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$829万
+$26,831/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$691万
+$27,297/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$525万
+$27,060/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$638万
+$25,612/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$633万
+$25,433/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$526万
+$18,929/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$601万
+$31,153/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1165万
+$27,934/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$689万
+$27,454/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$691万
+$27,437/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$493万
+$24,920/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$725万
+$23,464/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$679万
+$26,837/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$521万
+$26,879/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$653万
+$26,244/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$629万
+$25,257/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$617万
+$22,193/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$597万
+$30,946/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1123万
+$26,935/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$684万
+$27,270/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$687万
+$27,252/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$611万
+$30,861/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$818万
+$26,467/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$682万
+$26,941/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$518万
+$26,698/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$629万
+$25,268/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$631万
+$25,349/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$613万
+$22,043/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$576万
+$29,839/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1116万
+$26,751/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$694万
+$27,643/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$689万
+$27,352/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$607万
+$30,642/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$866万
+$28,042/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$677万
+$26,762/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$515万
+$26,522/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$631万
+$25,357/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$620万
+$24,910/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$600万
+$21,588/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$589万
+$30,518/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1108万
+$26,565/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$675万
+$26,891/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$692万
+$27,449/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$427万
+$21,554/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$835万
+$27,038/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$687万
+$27,142/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$516万
+$26,618/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$1751万
+$70,317/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$622万
+$24,999/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$663万
+$23,856/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$586万
+$30,355/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1100万
+$26,380/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$670万
+$26,708/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$680万
+$26,979/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$455万
+$22,980/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$821万
+$26,398/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$661万
+$26,131/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$508万
+$26,184/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 248呎 (1房)
+$636万
+$25,630/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$612万
+$24,563/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$642万
+$23,094/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$570万
+$29,531/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1092万
+$26,196/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$666万
+$26,517/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$675万
+$26,796/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$588万
+$29,690/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$815万
+$26,218/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$677万
+$26,778/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$504万
+$25,993/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$631万
+$25,346/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$614万
+$24,648/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$638万
+$22,934/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$566万
+$29,327/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1085万
+$26,010/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$663万
+$26,425/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$673万
+$26,697/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 197呎 (开放式)
+$586万
+$29,739/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$818万
+$26,476/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$661万
+$26,140/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$502万
+$25,900/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$616万
+$24,744/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$605万
+$24,303/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$635万
+$22,853/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$562万
+$29,118/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1069万
+$25,639/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$658万
+$26,234/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$668万
+$26,507/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$447万
+$22,574/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$806万
+$25,929/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$657万
+$25,966/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$504万
+$25,989/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$612万
+$24,567/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$620万
+$24,994/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$639万
+$22,987/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$544万
+$28,205/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1663万
+$39,889/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$654万
+$26,046/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$656万
+$26,050/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$438万
+$22,102/呎
+(23年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$795万
+$25,559/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$680万
+$26,858/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$495万
+$25,537/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$607万
+$24,393/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$596万
+$23,952/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$626万
+$22,532/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$538万
+$27,885/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1035万
+$24,823/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$649万
+$25,863/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$665万
+$26,406/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$573万
+$28,956/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$789万
+$25,371/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$648万
+$25,609/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$492万
+$25,361/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$645万
+$25,890/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$598万
+$24,031/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$630万
+$22,659/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$534万
+$27,681/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1028万
+$24,641/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$644万
+$25,671/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$654万
+$25,947/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 197呎 (开放式)
+$575万
+$29,195/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$783万
+$25,185/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$637万
+$25,166/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$489万
+$25,185/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$592万
+$23,792/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$588万
+$23,704/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$726万
+$26,100/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$525万
+$27,186/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1031万
+$24,714/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$652万
+$25,975/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$663万
+$26,301/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$533万
+$26,897/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$769万
+$24,900/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$639万
+$25,252/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$511万
+$26,325/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$594万
+$23,869/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$584万
+$23,437/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$720万
+$25,913/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$521万
+$26,984/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1023万
+$24,529/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$635万
+$25,297/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$644万
+$25,573/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$529万
+$26,701/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$772万
+$24,972/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$641万
+$25,335/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$492万
+$25,350/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$590万
+$23,692/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$579万
+$23,258/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$708万
+$25,455/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$517万
+$26,777/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1008万
+$24,183/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$646万
+$25,726/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$635万
+$25,216/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 197呎 (开放式)
+$532万
+$27,016/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$785万
+$25,401/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$632万
+$24,987/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$485万
+$25,000/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$582万
+$23,361/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$583万
+$23,512/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$713万
+$25,630/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$515万
+$26,674/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$762万
+$18,264/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$628万
+$25,014/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$637万
+$25,291/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$528万
+$26,681/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (1房)
+$763万
+$24,534/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$621万
+$24,546/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$482万
+$24,821/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 248呎 (1房)
+$583万
+$23,524/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$573万
+$23,002/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$707万
+$25,440/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$553万
+$28,661/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1129万
+$27,085/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$621万
+$24,734/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$630万
+$25,013/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$522万
+$26,376/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 309呎 (1房)
+$754万
+$24,410/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$621万
+$24,539/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$476万
+$24,544/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$645万
+$25,897/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$566万
+$22,739/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$699万
+$25,157/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$499万
+$25,847/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 379呎 (2房)
+$788万
+$20,792/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 229呎 (1房)
+$721万
+$31,480/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 230呎 (1房)
+$740万
+$32,167/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 175呎 (开放式)
+$480万
+$27,429/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 290呎 (1房)
+$680万
+$23,448/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 233呎 (1房)
+$610万
+$26,180/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 171呎 (开放式)
+$596万
+$34,837/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 227呎 (1房)
+$681万
+$30,005/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 227呎 (1房)
+$693万
+$30,511/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 257呎 (1房)
+$635万
+$24,708/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 171呎 (开放式)
+$618万
+$36,123/呎
+(22年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 632呎 (3房)
+$2000万
+$31,646/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 506呎 (3房)
+$1689万
+$33,375/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>C | 509呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 579呎 (3房)
+$1660万
+$28,670/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="22" t="inlineStr"/>
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="22" t="inlineStr"/>
+      <c r="L5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$951万
+$22,803/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$740万
+$29,496/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$739万
+$29,341/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$637万
+$32,160/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$766万
+$24,964/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$702万
+$27,747/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$550万
+$28,336/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$708万
+$28,449/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$751万
+$30,144/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$776万
+$27,926/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$383万
+$19,835/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1233万
+$29,575/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$724万
+$28,829/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$738万
+$29,291/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$629万
+$31,758/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$885万
+$28,815/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$701万
+$27,714/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$543万
+$27,993/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$707万
+$28,411/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$726万
+$29,162/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$767万
+$27,573/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$425万
+$22,002/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1127万
+$27,034/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$695万
+$27,679/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$709万
+$28,133/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$597万
+$30,141/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$848万
+$27,633/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$647万
+$25,556/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$517万
+$26,637/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$618万
+$24,817/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$647万
+$26,003/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$784万
+$28,203/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$527万
+$27,319/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1134万
+$27,199/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$660万
+$26,298/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$660万
+$26,179/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$589万
+$29,738/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$884万
+$28,782/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$642万
+$25,395/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$498万
+$25,655/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$614万
+$24,655/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$630万
+$25,307/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$643万
+$23,131/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$524万
+$27,141/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1098万
+$26,334/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$645万
+$25,687/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$644万
+$25,575/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$553万
+$27,947/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$881万
+$28,700/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$645万
+$25,495/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$500万
+$25,762/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$610万
+$24,493/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$619万
+$24,972/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$766万
+$27,543/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$526万
+$27,248/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1072万
+$25,716/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$650万
+$25,878/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$643万
+$25,505/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$546万
+$27,568/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$869万
+$28,217/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$634万
+$25,068/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$491万
+$25,327/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$600万
+$24,078/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$615万
+$24,708/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$761万
+$27,362/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$517万
+$26,792/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1065万
+$25,541/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$625万
+$24,920/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$632万
+$25,073/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 197呎 (开放式)
+$542万
+$27,518/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$881万
+$28,608/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$637万
+$25,169/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$488万
+$25,160/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$596万
+$23,918/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$618万
+$24,802/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$727万
+$26,151/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$514万
+$26,615/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1069万
+$25,635/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$621万
+$24,749/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$628万
+$24,907/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$538万
+$27,190/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$866万
+$28,124/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$633万
+$25,006/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$485万
+$24,999/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$592万
+$23,758/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$607万
+$24,376/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$715万
+$25,705/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$516万
+$26,716/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1051万
+$25,194/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$617万
+$24,583/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$630万
+$25,002/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 197呎 (开放式)
+$529万
+$26,856/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$869万
+$28,305/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$622万
+$24,584/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$507万
+$26,139/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 248呎 (1房)
+$594万
+$23,942/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$622万
+$24,976/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$710万
+$25,527/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$507万
+$26,260/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$994万
+$23,834/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$619万
+$24,673/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$626万
+$24,830/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$525万
+$26,533/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$812万
+$26,366/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$624万
+$24,679/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$484万
+$24,925/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$584万
+$23,437/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$599万
+$24,141/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$712万
+$25,620/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$503万
+$26,083/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$977万
+$23,424/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$609万
+$24,250/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$694万
+$27,543/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$538万
+$27,178/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$815万
+$26,542/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$620万
+$24,512/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$490万
+$25,278/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$580万
+$23,273/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$601万
+$24,127/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$667万
+$23,983/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$500万
+$25,911/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$1001万
+$23,995/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$611万
+$24,337/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$611万
+$24,240/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$523万
+$26,434/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$809万
+$26,358/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$610万
+$24,099/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$472万
+$24,338/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$576万
+$23,113/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$590万
+$23,712/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$662万
+$23,814/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$502万
+$26,005/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$973万
+$23,339/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$639万
+$25,461/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$615万
+$24,411/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$521万
+$26,337/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$795万
+$25,807/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$608万
+$24,013/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$475万
+$24,510/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$580万
+$23,275/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$588万
+$23,628/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$660万
+$23,731/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$498万
+$25,825/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$953万
+$22,852/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$652万
+$25,988/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$611万
+$24,244/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$518万
+$26,148/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$794万
+$25,795/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$610万
+$24,102/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$482万
+$24,849/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$570万
+$22,872/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$582万
+$23,474/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$650万
+$23,396/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$505万
+$26,181/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$953万
+$22,847/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$626万
+$24,927/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$607万
+$24,072/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$509万
+$25,688/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$741万
+$24,050/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$599万
+$23,690/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$479万
+$24,682/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$566万
+$22,712/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$576万
+$23,225/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$641万
+$23,061/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$486万
+$25,202/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$936万
+$22,445/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$603万
+$24,030/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$594万
+$23,573/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$508万
+$25,678/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 307呎 (1房)
+$735万
+$23,950/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$595万
+$23,528/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$461万
+$23,760/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$562万
+$22,552/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$590万
+$23,685/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$636万
+$22,895/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$483万
+$25,030/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$929万
+$22,281/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$599万
+$23,856/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$588万
+$23,324/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$498万
+$25,127/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$722万
+$23,451/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$591万
+$23,367/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$458万
+$23,593/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$558万
+$22,392/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$574万
+$23,036/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$625万
+$22,492/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$490万
+$25,376/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$932万
+$22,352/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$594万
+$23,682/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$590万
+$23,402/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$494万
+$24,940/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$717万
+$23,275/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$587万
+$23,202/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$455万
+$23,432/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 248呎 (1房)
+$559万
+$22,556/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$564万
+$22,632/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$621万
+$22,325/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$469万
+$24,326/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$925万
+$22,186/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$596万
+$23,759/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$585万
+$23,230/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$495万
+$25,013/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$719万
+$23,342/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$583万
+$23,040/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$456万
+$23,510/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$550万
+$22,071/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$565万
+$22,701/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$636万
+$22,861/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$459万
+$23,794/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$941万
+$22,566/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$594万
+$23,671/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$595万
+$23,629/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$488万
+$24,657/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$709万
+$23,010/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$581万
+$22,961/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$450万
+$23,182/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 248呎 (1房)
+$548万
+$22,080/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$575万
+$23,087/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$620万
+$22,308/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$458万
+$23,706/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$911万
+$21,857/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$584万
+$23,254/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$573万
+$22,740/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$490万
+$24,727/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$711万
+$23,077/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$577万
+$22,800/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$446万
+$23,015/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$588万
+$23,609/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 249呎 (1房)
+$553万
+$22,216/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$646万
+$23,248/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$496万
+$25,716/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 417呎 (2房)
+$920万
+$22,061/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 251呎 (1房)
+$595万
+$23,719/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 252呎 (1房)
+$567万
+$22,491/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 198呎 (开放式)
+$479万
+$24,196/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+$717万
+$23,285/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 253呎 (1房)
+$578万
+$22,839/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 194呎 (开放式)
+$442万
+$22,771/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 249呎 (1房)
+$587万
+$23,591/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 248呎 (1房)
+$548万
+$22,091/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 278呎 (1房)
+$646万
+$23,226/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 193呎 (开放式)
+$491万
+$25,428/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 379呎 (2房)
+$1170万
+$30,872/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 230呎 (1房)
+$700万
+$30,451/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 230呎 (1房)
+$721万
+$31,359/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 175呎 (开放式)
+$398万
+$22,743/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 286呎 (1房)
+$700万
+$24,476/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 233呎 (1房)
+$628万
+$26,953/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 171呎 (开放式)
+$450万
+$26,316/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 227呎 (1房)
+$693万
+$30,521/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 227呎 (1房)
+$716万
+$31,522/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 257呎 (1房)
+$720万
+$28,016/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 171呎 (开放式)
+$380万
+$22,222/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-旺角-利奥坊．凯岸.xlsx
+++ b/files/九龙-旺角-利奥坊．凯岸.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-旺角-利奥坊．凯岸.xlsx
+++ b/files/九龙-旺角-利奥坊．凯岸.xlsx
@@ -32810,7 +32810,7 @@
           <t>B | 508呎 (3房)
 $1708万
 $33,622/呎
-(22年-09月-22日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -32818,7 +32818,7 @@
           <t>C | 509呎 (3房)
 $1300万
 $25,540/呎
-(24年-06月-18日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -32826,7 +32826,7 @@
           <t>D | 579呎 (3房)
 $1388万
 $23,972/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -32848,7 +32848,7 @@
           <t>A | 417呎 (2房)
 $1079万
 $25,877/呎
-(23年-07月-18日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -32856,7 +32856,7 @@
           <t>B | 251呎 (1房)
 $736万
 $29,341/呎
-(21年-08月-08日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -32864,7 +32864,7 @@
           <t>C | 252呎 (1房)
 $746万
 $29,589/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -32872,7 +32872,7 @@
           <t>D | 198呎 (开放式)
 $638万
 $32,227/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -32880,7 +32880,7 @@
           <t>E | 309呎 (1房)
 $801万
 $25,934/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -32888,7 +32888,7 @@
           <t>F | 253呎 (1房)
 $705万
 $27,861/呎
-(21年-11月-18日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -32896,7 +32896,7 @@
           <t>G | 194呎 (开放式)
 $448万
 $23,088/呎
-(23年-09月-28日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -32904,7 +32904,7 @@
           <t>H | 249呎 (1房)
 $698万
 $28,012/呎
-(21年-11月-29日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -32912,7 +32912,7 @@
           <t>J | 249呎 (1房)
 $693万
 $27,849/呎
-(21年-11月-29日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -32920,7 +32920,7 @@
           <t>K | 278呎 (1房)
 $576万
 $20,730/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -32928,7 +32928,7 @@
           <t>L | 193呎 (开放式)
 $605万
 $31,332/呎
-(21年-10月-27日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -32943,7 +32943,7 @@
           <t>A | 417呎 (2房)
 $986万
 $23,646/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -32951,7 +32951,7 @@
           <t>B | 251呎 (1房)
 $727万
 $28,983/呎
-(21年-08月-03日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -32959,7 +32959,7 @@
           <t>C | 252呎 (1房)
 $745万
 $29,557/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -32967,7 +32967,7 @@
           <t>D | 198呎 (开放式)
 $637万
 $32,181/呎
-(21年-10月-14日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -32975,7 +32975,7 @@
           <t>E | 309呎 (1房)
 $899万
 $29,091/呎
-(21年-11月-12日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -32983,7 +32983,7 @@
           <t>F | 253呎 (1房)
 $696万
 $27,523/呎
-(21年-11月-09日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -32991,7 +32991,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $25,019/呎
-(23年-04月-17日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -32999,7 +32999,7 @@
           <t>H | 249呎 (1房)
 $696万
 $27,969/呎
-(21年-10月-14日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -33007,7 +33007,7 @@
           <t>J | 249呎 (1房)
 $692万
 $27,801/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -33015,7 +33015,7 @@
           <t>K | 278呎 (1房)
 $569万
 $20,471/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -33023,7 +33023,7 @@
           <t>L | 193呎 (开放式)
 $597万
 $30,936/呎
-(21年-11月-15日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33038,7 @@
           <t>A | 417呎 (2房)
 $1173万
 $28,122/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -33046,7 +33046,7 @@
           <t>B | 251呎 (1房)
 $722万
 $28,773/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -33054,7 +33054,7 @@
           <t>C | 252呎 (1房)
 $724万
 $28,738/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -33062,7 +33062,7 @@
           <t>D | 198呎 (开放式)
 $643万
 $32,475/呎
-(18年-08月-21日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -33070,7 +33070,7 @@
           <t>E | 309呎 (1房)
 $863万
 $27,915/呎
-(21年-09月-13日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -33078,7 +33078,7 @@
           <t>F | 253呎 (1房)
 $704万
 $27,832/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -33086,7 +33086,7 @@
           <t>G | 194呎 (开放式)
 $535万
 $27,589/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -33094,7 +33094,7 @@
           <t>H | 249呎 (1房)
 $685万
 $27,510/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -33102,7 +33102,7 @@
           <t>J | 248呎 (1房)
 $653万
 $26,334/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -33110,7 +33110,7 @@
           <t>K | 278呎 (1房)
 $546万
 $19,630/呎
-(24年-03月-07日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -33118,7 +33118,7 @@
           <t>L | 193呎 (开放式)
 $620万
 $32,118/呎
-(18年-07月-06日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33133,7 +33133,7 @@
           <t>A | 417呎 (2房)
 $1157万
 $27,755/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -33141,7 +33141,7 @@
           <t>B | 251呎 (1房)
 $713万
 $28,398/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -33149,7 +33149,7 @@
           <t>C | 252呎 (1房)
 $730万
 $28,961/呎
-(18年-07月-26日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -33157,7 +33157,7 @@
           <t>D | 198呎 (开放式)
 $597万
 $30,127/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -33165,7 +33165,7 @@
           <t>E | 309呎 (1房)
 $861万
 $27,860/呎
-(21年-12月-16日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -33173,7 +33173,7 @@
           <t>F | 253呎 (1房)
 $714万
 $28,230/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -33181,7 +33181,7 @@
           <t>G | 194呎 (开放式)
 $537万
 $27,701/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -33189,7 +33189,7 @@
           <t>H | 249呎 (1房)
 $653万
 $26,236/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -33197,7 +33197,7 @@
           <t>J | 249呎 (1房)
 $649万
 $26,051/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -33205,7 +33205,7 @@
           <t>K | 278呎 (1房)
 $533万
 $19,186/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -33213,7 +33213,7 @@
           <t>L | 193呎 (开放式)
 $616万
 $31,904/呎
-(18年-07月-23日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33228,7 +33228,7 @@
           <t>A | 417呎 (2房)
 $1154万
 $27,679/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -33236,7 +33236,7 @@
           <t>B | 251呎 (1房)
 $703万
 $28,024/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -33244,7 +33244,7 @@
           <t>C | 252呎 (1房)
 $705万
 $27,995/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -33252,7 +33252,7 @@
           <t>D | 198呎 (开放式)
 $595万
 $30,058/呎
-(21年-10月-16日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -33260,7 +33260,7 @@
           <t>E | 309呎 (1房)
 $849万
 $27,491/呎
-(22年-02月-24日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -33268,7 +33268,7 @@
           <t>F | 253呎 (1房)
 $688万
 $27,193/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -33276,7 +33276,7 @@
           <t>G | 194呎 (开放式)
 $534万
 $27,523/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -33284,7 +33284,7 @@
           <t>H | 249呎 (1房)
 $642万
 $25,787/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -33292,7 +33292,7 @@
           <t>J | 249呎 (1房)
 $638万
 $25,604/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -33300,7 +33300,7 @@
           <t>K | 278呎 (1房)
 $530万
 $19,059/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -33308,7 +33308,7 @@
           <t>L | 193呎 (开放式)
 $612万
 $31,695/呎
-(18年-07月-22日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33323,7 +33323,7 @@
           <t>A | 417呎 (2房)
 $1161万
 $27,835/呎
-(18年-07月-25日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -33331,7 +33331,7 @@
           <t>B | 251呎 (1房)
 $687万
 $27,357/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -33339,7 +33339,7 @@
           <t>C | 252呎 (1房)
 $711万
 $28,207/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -33347,7 +33347,7 @@
           <t>D | 198呎 (开放式)
 $587万
 $29,653/呎
-(21年-10月-19日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -33355,7 +33355,7 @@
           <t>E | 309呎 (1房)
 $829万
 $26,831/呎
-(22年-05月-11日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -33363,7 +33363,7 @@
           <t>F | 253呎 (1房)
 $691万
 $27,297/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -33371,7 +33371,7 @@
           <t>G | 194呎 (开放式)
 $525万
 $27,060/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -33379,7 +33379,7 @@
           <t>H | 249呎 (1房)
 $638万
 $25,612/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -33387,7 +33387,7 @@
           <t>J | 249呎 (1房)
 $633万
 $25,433/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -33395,7 +33395,7 @@
           <t>K | 278呎 (1房)
 $526万
 $18,929/呎
-(24年-03月-11日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -33403,7 +33403,7 @@
           <t>L | 193呎 (开放式)
 $601万
 $31,153/呎
-(18年-07月-26日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33418,7 +33418,7 @@
           <t>A | 417呎 (2房)
 $1165万
 $27,934/呎
-(18年-07月-25日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -33426,7 +33426,7 @@
           <t>B | 251呎 (1房)
 $689万
 $27,454/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -33434,7 +33434,7 @@
           <t>C | 252呎 (1房)
 $691万
 $27,437/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -33442,7 +33442,7 @@
           <t>D | 198呎 (开放式)
 $493万
 $24,920/呎
-(23年-06月-04日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -33450,7 +33450,7 @@
           <t>E | 309呎 (1房)
 $725万
 $23,464/呎
-(22年-12月-21日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -33458,7 +33458,7 @@
           <t>F | 253呎 (1房)
 $679万
 $26,837/呎
-(18年-06月-22日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -33466,7 +33466,7 @@
           <t>G | 194呎 (开放式)
 $521万
 $26,879/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -33474,7 +33474,7 @@
           <t>H | 249呎 (1房)
 $653万
 $26,244/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -33482,7 +33482,7 @@
           <t>J | 249呎 (1房)
 $629万
 $25,257/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -33490,7 +33490,7 @@
           <t>K | 278呎 (1房)
 $617万
 $22,193/呎
-(23年-09月-13日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -33498,7 +33498,7 @@
           <t>L | 193呎 (开放式)
 $597万
 $30,946/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33513,7 +33513,7 @@
           <t>A | 417呎 (2房)
 $1123万
 $26,935/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -33521,7 +33521,7 @@
           <t>B | 251呎 (1房)
 $684万
 $27,270/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -33529,7 +33529,7 @@
           <t>C | 252呎 (1房)
 $687万
 $27,252/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -33537,7 +33537,7 @@
           <t>D | 198呎 (开放式)
 $611万
 $30,861/呎
-(18年-10月-22日)</t>
+(18年-10月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -33545,7 +33545,7 @@
           <t>E | 309呎 (1房)
 $818万
 $26,467/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -33553,7 +33553,7 @@
           <t>F | 253呎 (1房)
 $682万
 $26,941/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -33561,7 +33561,7 @@
           <t>G | 194呎 (开放式)
 $518万
 $26,698/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -33569,7 +33569,7 @@
           <t>H | 249呎 (1房)
 $629万
 $25,268/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -33577,7 +33577,7 @@
           <t>J | 249呎 (1房)
 $631万
 $25,349/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -33585,7 +33585,7 @@
           <t>K | 278呎 (1房)
 $613万
 $22,043/呎
-(23年-08月-30日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -33593,7 +33593,7 @@
           <t>L | 193呎 (开放式)
 $576万
 $29,839/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33608,7 +33608,7 @@
           <t>A | 417呎 (2房)
 $1116万
 $26,751/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -33616,7 +33616,7 @@
           <t>B | 251呎 (1房)
 $694万
 $27,643/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -33624,7 +33624,7 @@
           <t>C | 252呎 (1房)
 $689万
 $27,352/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -33632,7 +33632,7 @@
           <t>D | 198呎 (开放式)
 $607万
 $30,642/呎
-(19年-08月-15日)</t>
+(19年-08月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -33640,7 +33640,7 @@
           <t>E | 309呎 (1房)
 $866万
 $28,042/呎
-(18年-09月-05日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -33648,7 +33648,7 @@
           <t>F | 253呎 (1房)
 $677万
 $26,762/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -33656,7 +33656,7 @@
           <t>G | 194呎 (开放式)
 $515万
 $26,522/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -33664,7 +33664,7 @@
           <t>H | 249呎 (1房)
 $631万
 $25,357/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -33672,7 +33672,7 @@
           <t>J | 249呎 (1房)
 $620万
 $24,910/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -33680,7 +33680,7 @@
           <t>K | 278呎 (1房)
 $600万
 $21,588/呎
-(23年-11月-13日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -33688,7 +33688,7 @@
           <t>L | 193呎 (开放式)
 $589万
 $30,518/呎
-(18年-07月-30日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33703,7 +33703,7 @@
           <t>A | 417呎 (2房)
 $1108万
 $26,565/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -33711,7 +33711,7 @@
           <t>B | 251呎 (1房)
 $675万
 $26,891/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -33719,7 +33719,7 @@
           <t>C | 252呎 (1房)
 $692万
 $27,449/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -33727,7 +33727,7 @@
           <t>D | 198呎 (开放式)
 $427万
 $21,554/呎
-(23年-10月-29日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -33735,7 +33735,7 @@
           <t>E | 309呎 (1房)
 $835万
 $27,038/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -33743,7 +33743,7 @@
           <t>F | 253呎 (1房)
 $687万
 $27,142/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -33751,7 +33751,7 @@
           <t>G | 194呎 (开放式)
 $516万
 $26,618/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -33759,7 +33759,7 @@
           <t>H | 249呎 (1房)
 $1751万
 $70,317/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -33767,7 +33767,7 @@
           <t>J | 249呎 (1房)
 $622万
 $24,999/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -33775,7 +33775,7 @@
           <t>K | 278呎 (1房)
 $663万
 $23,856/呎
-(23年-07月-30日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -33783,7 +33783,7 @@
           <t>L | 193呎 (开放式)
 $586万
 $30,355/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33798,7 +33798,7 @@
           <t>A | 417呎 (2房)
 $1100万
 $26,380/呎
-(18年-07月-15日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -33806,7 +33806,7 @@
           <t>B | 251呎 (1房)
 $670万
 $26,708/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -33814,7 +33814,7 @@
           <t>C | 252呎 (1房)
 $680万
 $26,979/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -33822,7 +33822,7 @@
           <t>D | 198呎 (开放式)
 $455万
 $22,980/呎
-(23年-08月-30日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -33830,7 +33830,7 @@
           <t>E | 311呎 (1房)
 $821万
 $26,398/呎
-(18年-06月-22日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -33838,7 +33838,7 @@
           <t>F | 253呎 (1房)
 $661万
 $26,131/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -33846,7 +33846,7 @@
           <t>G | 194呎 (开放式)
 $508万
 $26,184/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -33854,7 +33854,7 @@
           <t>H | 249呎 (1房)
 $636万
 $25,527/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -33862,7 +33862,7 @@
           <t>J | 249呎 (1房)
 $612万
 $24,563/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -33870,7 +33870,7 @@
           <t>K | 278呎 (1房)
 $642万
 $23,094/呎
-(23年-04月-10日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -33878,7 +33878,7 @@
           <t>L | 193呎 (开放式)
 $570万
 $29,531/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33893,7 +33893,7 @@
           <t>A | 417呎 (2房)
 $1092万
 $26,196/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -33901,7 +33901,7 @@
           <t>B | 251呎 (1房)
 $666万
 $26,517/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -33909,7 +33909,7 @@
           <t>C | 252呎 (1房)
 $675万
 $26,796/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -33917,7 +33917,7 @@
           <t>D | 198呎 (开放式)
 $588万
 $29,690/呎
-(18年-08月-27日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -33925,7 +33925,7 @@
           <t>E | 311呎 (1房)
 $815万
 $26,218/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -33933,7 +33933,7 @@
           <t>F | 253呎 (1房)
 $677万
 $26,778/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -33941,7 +33941,7 @@
           <t>G | 194呎 (开放式)
 $504万
 $25,993/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -33949,7 +33949,7 @@
           <t>H | 249呎 (1房)
 $631万
 $25,346/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -33957,7 +33957,7 @@
           <t>J | 249呎 (1房)
 $614万
 $24,648/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -33965,7 +33965,7 @@
           <t>K | 278呎 (1房)
 $638万
 $22,934/呎
-(23年-04月-13日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -33973,7 +33973,7 @@
           <t>L | 193呎 (开放式)
 $566万
 $29,327/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -33988,7 +33988,7 @@
           <t>A | 417呎 (2房)
 $1085万
 $26,010/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -33996,7 +33996,7 @@
           <t>B | 251呎 (1房)
 $663万
 $26,425/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -34004,7 +34004,7 @@
           <t>C | 252呎 (1房)
 $673万
 $26,697/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -34012,7 +34012,7 @@
           <t>D | 197呎 (开放式)
 $586万
 $29,739/呎
-(18年-08月-23日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -34020,7 +34020,7 @@
           <t>E | 309呎 (1房)
 $818万
 $26,476/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>F | 253呎 (1房)
 $661万
 $26,140/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>G | 194呎 (开放式)
 $502万
 $25,900/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -34044,7 +34044,7 @@
           <t>H | 249呎 (1房)
 $616万
 $24,744/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -34052,7 +34052,7 @@
           <t>J | 249呎 (1房)
 $605万
 $24,303/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -34060,7 +34060,7 @@
           <t>K | 278呎 (1房)
 $635万
 $22,853/呎
-(23年-08月-01日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -34068,7 +34068,7 @@
           <t>L | 193呎 (开放式)
 $562万
 $29,118/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34083,7 +34083,7 @@
           <t>A | 417呎 (2房)
 $1069万
 $25,639/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -34091,7 +34091,7 @@
           <t>B | 251呎 (1房)
 $658万
 $26,234/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -34099,7 +34099,7 @@
           <t>C | 252呎 (1房)
 $668万
 $26,507/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -34107,7 +34107,7 @@
           <t>D | 198呎 (开放式)
 $447万
 $22,574/呎
-(23年-09月-27日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -34115,7 +34115,7 @@
           <t>E | 311呎 (1房)
 $806万
 $25,929/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -34123,7 +34123,7 @@
           <t>F | 253呎 (1房)
 $657万
 $25,966/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -34131,7 +34131,7 @@
           <t>G | 194呎 (开放式)
 $504万
 $25,989/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -34139,7 +34139,7 @@
           <t>H | 249呎 (1房)
 $612万
 $24,567/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -34147,7 +34147,7 @@
           <t>J | 248呎 (1房)
 $620万
 $24,994/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -34155,7 +34155,7 @@
           <t>K | 278呎 (1房)
 $639万
 $22,987/呎
-(23年-05月-14日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -34163,7 +34163,7 @@
           <t>L | 193呎 (开放式)
 $544万
 $28,205/呎
-(18年-06月-22日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
           <t>A | 417呎 (2房)
 $1663万
 $39,889/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -34186,7 +34186,7 @@
           <t>B | 251呎 (1房)
 $654万
 $26,046/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -34194,7 +34194,7 @@
           <t>C | 252呎 (1房)
 $656万
 $26,050/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -34202,7 +34202,7 @@
           <t>D | 198呎 (开放式)
 $438万
 $22,102/呎
-(23年-09月-03日)</t>
+(23年-09月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -34210,7 +34210,7 @@
           <t>E | 311呎 (1房)
 $795万
 $25,559/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -34218,7 +34218,7 @@
           <t>F | 253呎 (1房)
 $680万
 $26,858/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -34226,7 +34226,7 @@
           <t>G | 194呎 (开放式)
 $495万
 $25,537/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -34234,7 +34234,7 @@
           <t>H | 249呎 (1房)
 $607万
 $24,393/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -34242,7 +34242,7 @@
           <t>J | 249呎 (1房)
 $596万
 $23,952/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -34250,7 +34250,7 @@
           <t>K | 278呎 (1房)
 $626万
 $22,532/呎
-(23年-05月-03日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -34258,7 +34258,7 @@
           <t>L | 193呎 (开放式)
 $538万
 $27,885/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34273,7 +34273,7 @@
           <t>A | 417呎 (2房)
 $1035万
 $24,823/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -34281,7 +34281,7 @@
           <t>B | 251呎 (1房)
 $649万
 $25,863/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -34289,7 +34289,7 @@
           <t>C | 252呎 (1房)
 $665万
 $26,406/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -34297,7 +34297,7 @@
           <t>D | 198呎 (开放式)
 $573万
 $28,956/呎
-(18年-09月-03日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -34305,7 +34305,7 @@
           <t>E | 311呎 (1房)
 $789万
 $25,371/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -34313,7 +34313,7 @@
           <t>F | 253呎 (1房)
 $648万
 $25,609/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -34321,7 +34321,7 @@
           <t>G | 194呎 (开放式)
 $492万
 $25,361/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -34329,7 +34329,7 @@
           <t>H | 249呎 (1房)
 $645万
 $25,890/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -34337,7 +34337,7 @@
           <t>J | 249呎 (1房)
 $598万
 $24,031/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -34345,7 +34345,7 @@
           <t>K | 278呎 (1房)
 $630万
 $22,659/呎
-(23年-04月-11日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -34353,7 +34353,7 @@
           <t>L | 193呎 (开放式)
 $534万
 $27,681/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34368,7 @@
           <t>A | 417呎 (2房)
 $1028万
 $24,641/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -34376,7 +34376,7 @@
           <t>B | 251呎 (1房)
 $644万
 $25,671/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -34384,7 +34384,7 @@
           <t>C | 252呎 (1房)
 $654万
 $25,947/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -34392,7 +34392,7 @@
           <t>D | 197呎 (开放式)
 $575万
 $29,195/呎
-(18年-08月-21日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -34400,7 +34400,7 @@
           <t>E | 311呎 (1房)
 $783万
 $25,185/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -34408,7 +34408,7 @@
           <t>F | 253呎 (1房)
 $637万
 $25,166/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -34416,7 +34416,7 @@
           <t>G | 194呎 (开放式)
 $489万
 $25,185/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -34424,7 +34424,7 @@
           <t>H | 249呎 (1房)
 $592万
 $23,792/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -34432,7 +34432,7 @@
           <t>J | 248呎 (1房)
 $588万
 $23,704/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -34440,7 +34440,7 @@
           <t>K | 278呎 (1房)
 $726万
 $26,100/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -34448,7 +34448,7 @@
           <t>L | 193呎 (开放式)
 $525万
 $27,186/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34463,7 +34463,7 @@
           <t>A | 417呎 (2房)
 $1031万
 $24,714/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -34471,7 +34471,7 @@
           <t>B | 251呎 (1房)
 $652万
 $25,975/呎
-(19年-07月-09日)</t>
+(19年-07月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -34479,7 +34479,7 @@
           <t>C | 252呎 (1房)
 $663万
 $26,301/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -34487,7 +34487,7 @@
           <t>D | 198呎 (开放式)
 $533万
 $26,897/呎
-(18年-07月-15日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -34495,7 +34495,7 @@
           <t>E | 309呎 (1房)
 $769万
 $24,900/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -34503,7 +34503,7 @@
           <t>F | 253呎 (1房)
 $639万
 $25,252/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -34511,7 +34511,7 @@
           <t>G | 194呎 (开放式)
 $511万
 $26,325/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -34519,7 +34519,7 @@
           <t>H | 249呎 (1房)
 $594万
 $23,869/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -34527,7 +34527,7 @@
           <t>J | 249呎 (1房)
 $584万
 $23,437/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -34535,7 +34535,7 @@
           <t>K | 278呎 (1房)
 $720万
 $25,913/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -34543,7 +34543,7 @@
           <t>L | 193呎 (开放式)
 $521万
 $26,984/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34558,7 +34558,7 @@
           <t>A | 417呎 (2房)
 $1023万
 $24,529/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -34566,7 +34566,7 @@
           <t>B | 251呎 (1房)
 $635万
 $25,297/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -34574,7 +34574,7 @@
           <t>C | 252呎 (1房)
 $644万
 $25,573/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -34582,7 +34582,7 @@
           <t>D | 198呎 (开放式)
 $529万
 $26,701/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -34590,7 +34590,7 @@
           <t>E | 309呎 (1房)
 $772万
 $24,972/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -34598,7 +34598,7 @@
           <t>F | 253呎 (1房)
 $641万
 $25,335/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -34606,7 +34606,7 @@
           <t>G | 194呎 (开放式)
 $492万
 $25,350/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -34614,7 +34614,7 @@
           <t>H | 249呎 (1房)
 $590万
 $23,692/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -34622,7 +34622,7 @@
           <t>J | 249呎 (1房)
 $579万
 $23,258/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -34630,7 +34630,7 @@
           <t>K | 278呎 (1房)
 $708万
 $25,455/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -34638,7 +34638,7 @@
           <t>L | 193呎 (开放式)
 $517万
 $26,777/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
           <t>A | 417呎 (2房)
 $1008万
 $24,183/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -34661,7 +34661,7 @@
           <t>B | 251呎 (1房)
 $646万
 $25,726/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -34669,7 +34669,7 @@
           <t>C | 252呎 (1房)
 $635万
 $25,216/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -34677,7 +34677,7 @@
           <t>D | 197呎 (开放式)
 $532万
 $27,016/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -34685,7 +34685,7 @@
           <t>E | 309呎 (1房)
 $785万
 $25,401/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -34693,7 +34693,7 @@
           <t>F | 253呎 (1房)
 $632万
 $24,987/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -34701,7 +34701,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $25,000/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -34709,7 +34709,7 @@
           <t>H | 249呎 (1房)
 $582万
 $23,361/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -34717,7 +34717,7 @@
           <t>J | 248呎 (1房)
 $583万
 $23,512/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -34725,7 +34725,7 @@
           <t>K | 278呎 (1房)
 $713万
 $25,630/呎
-(18年-07月-15日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -34733,7 +34733,7 @@
           <t>L | 193呎 (开放式)
 $515万
 $26,674/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34748,7 +34748,7 @@
           <t>A | 417呎 (2房)
 $762万
 $18,264/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -34756,7 +34756,7 @@
           <t>B | 251呎 (1房)
 $628万
 $25,014/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -34764,7 +34764,7 @@
           <t>C | 252呎 (1房)
 $637万
 $25,291/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -34772,7 +34772,7 @@
           <t>D | 198呎 (开放式)
 $528万
 $26,681/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -34780,7 +34780,7 @@
           <t>E | 311呎 (1房)
 $763万
 $24,534/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -34788,7 +34788,7 @@
           <t>F | 253呎 (1房)
 $621万
 $24,546/呎
-(18年-06月-22日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -34796,7 +34796,7 @@
           <t>G | 194呎 (开放式)
 $482万
 $24,821/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -34804,7 +34804,7 @@
           <t>H | 248呎 (1房)
 $583万
 $23,524/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -34812,7 +34812,7 @@
           <t>J | 249呎 (1房)
 $573万
 $23,002/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -34820,7 +34820,7 @@
           <t>K | 278呎 (1房)
 $707万
 $25,440/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -34828,7 +34828,7 @@
           <t>L | 193呎 (开放式)
 $553万
 $28,661/呎
-(18年-07月-23日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34843,7 +34843,7 @@
           <t>A | 417呎 (2房)
 $1129万
 $27,085/呎
-(18年-09月-11日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -34851,7 +34851,7 @@
           <t>B | 251呎 (1房)
 $621万
 $24,734/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -34859,7 +34859,7 @@
           <t>C | 252呎 (1房)
 $630万
 $25,013/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -34867,7 +34867,7 @@
           <t>D | 198呎 (开放式)
 $522万
 $26,376/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -34875,7 +34875,7 @@
           <t>E | 309呎 (1房)
 $754万
 $24,410/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -34883,7 +34883,7 @@
           <t>F | 253呎 (1房)
 $621万
 $24,539/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -34891,7 +34891,7 @@
           <t>G | 194呎 (开放式)
 $476万
 $24,544/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -34899,7 +34899,7 @@
           <t>H | 249呎 (1房)
 $645万
 $25,897/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -34907,7 +34907,7 @@
           <t>J | 249呎 (1房)
 $566万
 $22,739/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -34915,7 +34915,7 @@
           <t>K | 278呎 (1房)
 $699万
 $25,157/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -34923,7 +34923,7 @@
           <t>L | 193呎 (开放式)
 $499万
 $25,847/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -34938,7 +34938,7 @@
           <t>A | 379呎 (2房)
 $788万
 $20,792/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -34946,7 +34946,7 @@
           <t>B | 229呎 (1房)
 $721万
 $31,480/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -34954,7 +34954,7 @@
           <t>C | 230呎 (1房)
 $740万
 $32,167/呎
-(22年-01月-17日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -34962,7 +34962,7 @@
           <t>D | 175呎 (开放式)
 $480万
 $27,429/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -34970,7 +34970,7 @@
           <t>E | 290呎 (1房)
 $680万
 $23,448/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -34978,7 +34978,7 @@
           <t>F | 233呎 (1房)
 $610万
 $26,180/呎
-(23年-07月-02日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -34986,7 +34986,7 @@
           <t>G | 171呎 (开放式)
 $596万
 $34,837/呎
-(22年-09月-22日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -34994,7 +34994,7 @@
           <t>H | 227呎 (1房)
 $681万
 $30,005/呎
-(21年-06月-08日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -35002,7 +35002,7 @@
           <t>J | 227呎 (1房)
 $693万
 $30,511/呎
-(21年-09月-19日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -35010,7 +35010,7 @@
           <t>K | 257呎 (1房)
 $635万
 $24,708/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -35018,7 +35018,7 @@
           <t>L | 171呎 (开放式)
 $618万
 $36,123/呎
-(22年-07月-13日)</t>
+(22年-07月)</t>
         </is>
       </c>
     </row>
@@ -35198,7 +35198,7 @@
           <t>A | 632呎 (3房)
 $2000万
 $31,646/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -35206,7 +35206,7 @@
           <t>B | 506呎 (3房)
 $1689万
 $33,375/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -35222,7 +35222,7 @@
           <t>D | 579呎 (3房)
 $1660万
 $28,670/呎
-(22年-10月-30日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -35244,7 +35244,7 @@
           <t>A | 417呎 (2房)
 $951万
 $22,803/呎
-(23年-12月-06日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -35252,7 +35252,7 @@
           <t>B | 251呎 (1房)
 $740万
 $29,496/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35260,7 +35260,7 @@
           <t>C | 252呎 (1房)
 $739万
 $29,341/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -35268,7 +35268,7 @@
           <t>D | 198呎 (开放式)
 $637万
 $32,160/呎
-(18年-09月-05日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -35276,7 +35276,7 @@
           <t>E | 307呎 (1房)
 $766万
 $24,964/呎
-(23年-04月-10日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -35284,7 +35284,7 @@
           <t>F | 253呎 (1房)
 $702万
 $27,747/呎
-(21年-11月-15日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -35292,7 +35292,7 @@
           <t>G | 194呎 (开放式)
 $550万
 $28,336/呎
-(21年-11月-29日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -35300,7 +35300,7 @@
           <t>H | 249呎 (1房)
 $708万
 $28,449/呎
-(21年-12月-20日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -35308,7 +35308,7 @@
           <t>J | 249呎 (1房)
 $751万
 $30,144/呎
-(18年-09月-27日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -35316,7 +35316,7 @@
           <t>K | 278呎 (1房)
 $776万
 $27,926/呎
-(22年-04月-25日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -35324,7 +35324,7 @@
           <t>L | 193呎 (开放式)
 $383万
 $19,835/呎
-(25年-08月-27日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -35339,7 +35339,7 @@
           <t>A | 417呎 (2房)
 $1233万
 $29,575/呎
-(19年-05月-22日)</t>
+(19年-05月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -35347,7 +35347,7 @@
           <t>B | 251呎 (1房)
 $724万
 $28,829/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35355,7 +35355,7 @@
           <t>C | 252呎 (1房)
 $738万
 $29,291/呎
-(18年-07月-12日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -35363,7 +35363,7 @@
           <t>D | 198呎 (开放式)
 $629万
 $31,758/呎
-(18年-08月-16日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>E | 307呎 (1房)
 $885万
 $28,815/呎
-(21年-09月-02日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -35379,7 +35379,7 @@
           <t>F | 253呎 (1房)
 $701万
 $27,714/呎
-(21年-11月-03日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -35387,7 +35387,7 @@
           <t>G | 194呎 (开放式)
 $543万
 $27,993/呎
-(21年-12月-01日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -35395,7 +35395,7 @@
           <t>H | 249呎 (1房)
 $707万
 $28,411/呎
-(21年-11月-10日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -35403,7 +35403,7 @@
           <t>J | 249呎 (1房)
 $726万
 $29,162/呎
-(18年-09月-13日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -35411,7 +35411,7 @@
           <t>K | 278呎 (1房)
 $767万
 $27,573/呎
-(22年-03月-01日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -35419,7 +35419,7 @@
           <t>L | 193呎 (开放式)
 $425万
 $22,002/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -35434,7 +35434,7 @@
           <t>A | 417呎 (2房)
 $1127万
 $27,034/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -35442,7 +35442,7 @@
           <t>B | 251呎 (1房)
 $695万
 $27,679/呎
-(18年-07月-24日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35450,7 +35450,7 @@
           <t>C | 252呎 (1房)
 $709万
 $28,133/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -35458,7 +35458,7 @@
           <t>D | 198呎 (开放式)
 $597万
 $30,141/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -35466,7 +35466,7 @@
           <t>E | 307呎 (1房)
 $848万
 $27,633/呎
-(21年-10月-21日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -35474,7 +35474,7 @@
           <t>F | 253呎 (1房)
 $647万
 $25,556/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -35482,7 +35482,7 @@
           <t>G | 194呎 (开放式)
 $517万
 $26,637/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -35490,7 +35490,7 @@
           <t>H | 249呎 (1房)
 $618万
 $24,817/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -35498,7 +35498,7 @@
           <t>J | 249呎 (1房)
 $647万
 $26,003/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -35506,7 +35506,7 @@
           <t>K | 278呎 (1房)
 $784万
 $28,203/呎
-(18年-08月-15日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -35514,7 +35514,7 @@
           <t>L | 193呎 (开放式)
 $527万
 $27,319/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35529,7 @@
           <t>A | 417呎 (2房)
 $1134万
 $27,199/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -35537,7 +35537,7 @@
           <t>B | 251呎 (1房)
 $660万
 $26,298/呎
-(18年-06月-24日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -35545,7 +35545,7 @@
           <t>C | 252呎 (1房)
 $660万
 $26,179/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -35553,7 +35553,7 @@
           <t>D | 198呎 (开放式)
 $589万
 $29,738/呎
-(18年-06月-30日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -35561,7 +35561,7 @@
           <t>E | 307呎 (1房)
 $884万
 $28,782/呎
-(19年-06月-19日)</t>
+(19年-06月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -35569,7 +35569,7 @@
           <t>F | 253呎 (1房)
 $642万
 $25,395/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -35577,7 +35577,7 @@
           <t>G | 194呎 (开放式)
 $498万
 $25,655/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -35585,7 +35585,7 @@
           <t>H | 249呎 (1房)
 $614万
 $24,655/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -35593,7 +35593,7 @@
           <t>J | 249呎 (1房)
 $630万
 $25,307/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -35601,7 +35601,7 @@
           <t>K | 278呎 (1房)
 $643万
 $23,131/呎
-(23年-03月-08日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -35609,7 +35609,7 @@
           <t>L | 193呎 (开放式)
 $524万
 $27,141/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -35624,7 +35624,7 @@
           <t>A | 417呎 (2房)
 $1098万
 $26,334/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -35632,7 +35632,7 @@
           <t>B | 251呎 (1房)
 $645万
 $25,687/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -35640,7 +35640,7 @@
           <t>C | 252呎 (1房)
 $644万
 $25,575/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -35648,7 +35648,7 @@
           <t>D | 198呎 (开放式)
 $553万
 $27,947/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -35656,7 +35656,7 @@
           <t>E | 307呎 (1房)
 $881万
 $28,700/呎
-(18年-08月-21日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -35664,7 +35664,7 @@
           <t>F | 253呎 (1房)
 $645万
 $25,495/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -35672,7 +35672,7 @@
           <t>G | 194呎 (开放式)
 $500万
 $25,762/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -35680,7 +35680,7 @@
           <t>H | 249呎 (1房)
 $610万
 $24,493/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -35688,7 +35688,7 @@
           <t>J | 248呎 (1房)
 $619万
 $24,972/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -35696,7 +35696,7 @@
           <t>K | 278呎 (1房)
 $766万
 $27,543/呎
-(18年-08月-14日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -35704,7 +35704,7 @@
           <t>L | 193呎 (开放式)
 $526万
 $27,248/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35719,7 @@
           <t>A | 417呎 (2房)
 $1072万
 $25,716/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -35727,7 +35727,7 @@
           <t>B | 251呎 (1房)
 $650万
 $25,878/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -35735,7 +35735,7 @@
           <t>C | 252呎 (1房)
 $643万
 $25,505/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -35743,7 +35743,7 @@
           <t>D | 198呎 (开放式)
 $546万
 $27,568/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -35751,7 +35751,7 @@
           <t>E | 308呎 (1房)
 $869万
 $28,217/呎
-(18年-08月-13日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -35759,7 +35759,7 @@
           <t>F | 253呎 (1房)
 $634万
 $25,068/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -35767,7 +35767,7 @@
           <t>G | 194呎 (开放式)
 $491万
 $25,327/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -35775,7 +35775,7 @@
           <t>H | 249呎 (1房)
 $600万
 $24,078/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -35783,7 +35783,7 @@
           <t>J | 249呎 (1房)
 $615万
 $24,708/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -35791,7 +35791,7 @@
           <t>K | 278呎 (1房)
 $761万
 $27,362/呎
-(18年-07月-26日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -35799,7 +35799,7 @@
           <t>L | 193呎 (开放式)
 $517万
 $26,792/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
           <t>A | 417呎 (2房)
 $1065万
 $25,541/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -35822,7 +35822,7 @@
           <t>B | 251呎 (1房)
 $625万
 $24,920/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -35830,7 +35830,7 @@
           <t>C | 252呎 (1房)
 $632万
 $25,073/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -35838,7 +35838,7 @@
           <t>D | 197呎 (开放式)
 $542万
 $27,518/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -35846,7 +35846,7 @@
           <t>E | 308呎 (1房)
 $881万
 $28,608/呎
-(18年-07月-16日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -35854,7 +35854,7 @@
           <t>F | 253呎 (1房)
 $637万
 $25,169/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -35862,7 +35862,7 @@
           <t>G | 194呎 (开放式)
 $488万
 $25,160/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -35870,7 +35870,7 @@
           <t>H | 249呎 (1房)
 $596万
 $23,918/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -35878,7 +35878,7 @@
           <t>J | 249呎 (1房)
 $618万
 $24,802/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -35886,7 +35886,7 @@
           <t>K | 278呎 (1房)
 $727万
 $26,151/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -35894,7 +35894,7 @@
           <t>L | 193呎 (开放式)
 $514万
 $26,615/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35909,7 @@
           <t>A | 417呎 (2房)
 $1069万
 $25,635/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -35917,7 +35917,7 @@
           <t>B | 251呎 (1房)
 $621万
 $24,749/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -35925,7 +35925,7 @@
           <t>C | 252呎 (1房)
 $628万
 $24,907/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -35933,7 +35933,7 @@
           <t>D | 198呎 (开放式)
 $538万
 $27,190/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -35941,7 +35941,7 @@
           <t>E | 308呎 (1房)
 $866万
 $28,124/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -35949,7 +35949,7 @@
           <t>F | 253呎 (1房)
 $633万
 $25,006/呎
-(18年-06月-26日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -35957,7 +35957,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $24,999/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -35965,7 +35965,7 @@
           <t>H | 249呎 (1房)
 $592万
 $23,758/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -35973,7 +35973,7 @@
           <t>J | 249呎 (1房)
 $607万
 $24,376/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -35981,7 +35981,7 @@
           <t>K | 278呎 (1房)
 $715万
 $25,705/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -35989,7 +35989,7 @@
           <t>L | 193呎 (开放式)
 $516万
 $26,716/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36004,7 +36004,7 @@
           <t>A | 417呎 (2房)
 $1051万
 $25,194/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -36012,7 +36012,7 @@
           <t>B | 251呎 (1房)
 $617万
 $24,583/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -36020,7 +36020,7 @@
           <t>C | 252呎 (1房)
 $630万
 $25,002/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -36028,7 +36028,7 @@
           <t>D | 197呎 (开放式)
 $529万
 $26,856/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -36036,7 +36036,7 @@
           <t>E | 307呎 (1房)
 $869万
 $28,305/呎
-(18年-08月-20日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -36044,7 +36044,7 @@
           <t>F | 253呎 (1房)
 $622万
 $24,584/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -36052,7 +36052,7 @@
           <t>G | 194呎 (开放式)
 $507万
 $26,139/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -36060,7 +36060,7 @@
           <t>H | 248呎 (1房)
 $594万
 $23,942/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -36068,7 +36068,7 @@
           <t>J | 249呎 (1房)
 $622万
 $24,976/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -36076,7 +36076,7 @@
           <t>K | 278呎 (1房)
 $710万
 $25,527/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -36084,7 +36084,7 @@
           <t>L | 193呎 (开放式)
 $507万
 $26,260/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36099,7 +36099,7 @@
           <t>A | 417呎 (2房)
 $994万
 $23,834/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -36107,7 +36107,7 @@
           <t>B | 251呎 (1房)
 $619万
 $24,673/呎
-(18年-06月-24日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -36115,7 +36115,7 @@
           <t>C | 252呎 (1房)
 $626万
 $24,830/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -36123,7 +36123,7 @@
           <t>D | 198呎 (开放式)
 $525万
 $26,533/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -36131,7 +36131,7 @@
           <t>E | 308呎 (1房)
 $812万
 $26,366/呎
-(18年-06月-22日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -36139,7 +36139,7 @@
           <t>F | 253呎 (1房)
 $624万
 $24,679/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -36147,7 +36147,7 @@
           <t>G | 194呎 (开放式)
 $484万
 $24,925/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -36155,7 +36155,7 @@
           <t>H | 249呎 (1房)
 $584万
 $23,437/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -36163,7 +36163,7 @@
           <t>J | 248呎 (1房)
 $599万
 $24,141/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -36171,7 +36171,7 @@
           <t>K | 278呎 (1房)
 $712万
 $25,620/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -36179,7 +36179,7 @@
           <t>L | 193呎 (开放式)
 $503万
 $26,083/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36194,7 +36194,7 @@
           <t>A | 417呎 (2房)
 $977万
 $23,424/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -36202,7 +36202,7 @@
           <t>B | 251呎 (1房)
 $609万
 $24,250/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -36210,7 +36210,7 @@
           <t>C | 252呎 (1房)
 $694万
 $27,543/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -36218,7 +36218,7 @@
           <t>D | 198呎 (开放式)
 $538万
 $27,178/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -36226,7 +36226,7 @@
           <t>E | 307呎 (1房)
 $815万
 $26,542/呎
-(18年-07月-18日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -36234,7 +36234,7 @@
           <t>F | 253呎 (1房)
 $620万
 $24,512/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -36242,7 +36242,7 @@
           <t>G | 194呎 (开放式)
 $490万
 $25,278/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -36250,7 +36250,7 @@
           <t>H | 249呎 (1房)
 $580万
 $23,273/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -36258,7 +36258,7 @@
           <t>J | 249呎 (1房)
 $601万
 $24,127/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -36266,7 +36266,7 @@
           <t>K | 278呎 (1房)
 $667万
 $23,983/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -36274,7 +36274,7 @@
           <t>L | 193呎 (开放式)
 $500万
 $25,911/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36289,7 +36289,7 @@
           <t>A | 417呎 (2房)
 $1001万
 $23,995/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -36297,7 +36297,7 @@
           <t>B | 251呎 (1房)
 $611万
 $24,337/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -36305,7 +36305,7 @@
           <t>C | 252呎 (1房)
 $611万
 $24,240/呎
-(18年-06月-26日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -36313,7 +36313,7 @@
           <t>D | 198呎 (开放式)
 $523万
 $26,434/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -36321,7 +36321,7 @@
           <t>E | 307呎 (1房)
 $809万
 $26,358/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -36329,7 +36329,7 @@
           <t>F | 253呎 (1房)
 $610万
 $24,099/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -36337,7 +36337,7 @@
           <t>G | 194呎 (开放式)
 $472万
 $24,338/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -36345,7 +36345,7 @@
           <t>H | 249呎 (1房)
 $576万
 $23,113/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -36353,7 +36353,7 @@
           <t>J | 249呎 (1房)
 $590万
 $23,712/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -36361,7 +36361,7 @@
           <t>K | 278呎 (1房)
 $662万
 $23,814/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -36369,7 +36369,7 @@
           <t>L | 193呎 (开放式)
 $502万
 $26,005/呎
-(18年-07月-11日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36384,7 +36384,7 @@
           <t>A | 417呎 (2房)
 $973万
 $23,339/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -36392,7 +36392,7 @@
           <t>B | 251呎 (1房)
 $639万
 $25,461/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -36400,7 +36400,7 @@
           <t>C | 252呎 (1房)
 $615万
 $24,411/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -36408,7 +36408,7 @@
           <t>D | 198呎 (开放式)
 $521万
 $26,337/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -36416,7 +36416,7 @@
           <t>E | 308呎 (1房)
 $795万
 $25,807/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -36424,7 +36424,7 @@
           <t>F | 253呎 (1房)
 $608万
 $24,013/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -36432,7 +36432,7 @@
           <t>G | 194呎 (开放式)
 $475万
 $24,510/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -36440,7 +36440,7 @@
           <t>H | 249呎 (1房)
 $580万
 $23,275/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -36448,7 +36448,7 @@
           <t>J | 249呎 (1房)
 $588万
 $23,628/呎
-(18年-06月-24日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -36456,7 +36456,7 @@
           <t>K | 278呎 (1房)
 $660万
 $23,731/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -36464,7 +36464,7 @@
           <t>L | 193呎 (开放式)
 $498万
 $25,825/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36479,7 +36479,7 @@
           <t>A | 417呎 (2房)
 $953万
 $22,852/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -36487,7 +36487,7 @@
           <t>B | 251呎 (1房)
 $652万
 $25,988/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -36495,7 +36495,7 @@
           <t>C | 252呎 (1房)
 $611万
 $24,244/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -36503,7 +36503,7 @@
           <t>D | 198呎 (开放式)
 $518万
 $26,148/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -36511,7 +36511,7 @@
           <t>E | 308呎 (1房)
 $794万
 $25,795/呎
-(18年-06月-15日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -36519,7 +36519,7 @@
           <t>F | 253呎 (1房)
 $610万
 $24,102/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -36527,7 +36527,7 @@
           <t>G | 194呎 (开放式)
 $482万
 $24,849/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -36535,7 +36535,7 @@
           <t>H | 249呎 (1房)
 $570万
 $22,872/呎
-(18年-06月-26日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -36543,7 +36543,7 @@
           <t>J | 248呎 (1房)
 $582万
 $23,474/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -36551,7 +36551,7 @@
           <t>K | 278呎 (1房)
 $650万
 $23,396/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -36559,7 +36559,7 @@
           <t>L | 193呎 (开放式)
 $505万
 $26,181/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36574,7 +36574,7 @@
           <t>A | 417呎 (2房)
 $953万
 $22,847/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -36582,7 +36582,7 @@
           <t>B | 251呎 (1房)
 $626万
 $24,927/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -36590,7 +36590,7 @@
           <t>C | 252呎 (1房)
 $607万
 $24,072/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -36598,7 +36598,7 @@
           <t>D | 198呎 (开放式)
 $509万
 $25,688/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -36606,7 +36606,7 @@
           <t>E | 308呎 (1房)
 $741万
 $24,050/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -36614,7 +36614,7 @@
           <t>F | 253呎 (1房)
 $599万
 $23,690/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -36622,7 +36622,7 @@
           <t>G | 194呎 (开放式)
 $479万
 $24,682/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -36630,7 +36630,7 @@
           <t>H | 249呎 (1房)
 $566万
 $22,712/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -36638,7 +36638,7 @@
           <t>J | 248呎 (1房)
 $576万
 $23,225/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -36646,7 +36646,7 @@
           <t>K | 278呎 (1房)
 $641万
 $23,061/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -36654,7 +36654,7 @@
           <t>L | 193呎 (开放式)
 $486万
 $25,202/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -36669,7 +36669,7 @@
           <t>A | 417呎 (2房)
 $936万
 $22,445/呎
-(18年-06月-26日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -36677,7 +36677,7 @@
           <t>B | 251呎 (1房)
 $603万
 $24,030/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -36685,7 +36685,7 @@
           <t>C | 252呎 (1房)
 $594万
 $23,573/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -36693,7 +36693,7 @@
           <t>D | 198呎 (开放式)
 $508万
 $25,678/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -36701,7 +36701,7 @@
           <t>E | 307呎 (1房)
 $735万
 $23,950/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -36709,7 +36709,7 @@
           <t>F | 253呎 (1房)
 $595万
 $23,528/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -36717,7 +36717,7 @@
           <t>G | 194呎 (开放式)
 $461万
 $23,760/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -36725,7 +36725,7 @@
           <t>H | 249呎 (1房)
 $562万
 $22,552/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -36733,7 +36733,7 @@
           <t>J | 249呎 (1房)
 $590万
 $23,685/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -36741,7 +36741,7 @@
           <t>K | 278呎 (1房)
 $636万
 $22,895/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -36749,7 +36749,7 @@
           <t>L | 193呎 (开放式)
 $483万
 $25,030/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -36764,7 +36764,7 @@
           <t>A | 417呎 (2房)
 $929万
 $22,281/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -36772,7 +36772,7 @@
           <t>B | 251呎 (1房)
 $599万
 $23,856/呎
-(18年-06月-26日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -36780,7 +36780,7 @@
           <t>C | 252呎 (1房)
 $588万
 $23,324/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -36788,7 +36788,7 @@
           <t>D | 198呎 (开放式)
 $498万
 $25,127/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -36796,7 +36796,7 @@
           <t>E | 308呎 (1房)
 $722万
 $23,451/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -36804,7 +36804,7 @@
           <t>F | 253呎 (1房)
 $591万
 $23,367/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -36812,7 +36812,7 @@
           <t>G | 194呎 (开放式)
 $458万
 $23,593/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -36820,7 +36820,7 @@
           <t>H | 249呎 (1房)
 $558万
 $22,392/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -36828,7 +36828,7 @@
           <t>J | 249呎 (1房)
 $574万
 $23,036/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -36836,7 +36836,7 @@
           <t>K | 278呎 (1房)
 $625万
 $22,492/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -36844,7 +36844,7 @@
           <t>L | 193呎 (开放式)
 $490万
 $25,376/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -36859,7 +36859,7 @@
           <t>A | 417呎 (2房)
 $932万
 $22,352/呎
-(18年-06月-20日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -36867,7 +36867,7 @@
           <t>B | 251呎 (1房)
 $594万
 $23,682/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -36875,7 +36875,7 @@
           <t>C | 252呎 (1房)
 $590万
 $23,402/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -36883,7 +36883,7 @@
           <t>D | 198呎 (开放式)
 $494万
 $24,940/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -36891,7 +36891,7 @@
           <t>E | 308呎 (1房)
 $717万
 $23,275/呎
-(18年-10月-10日)</t>
+(18年-10月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -36899,7 +36899,7 @@
           <t>F | 253呎 (1房)
 $587万
 $23,202/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -36907,7 +36907,7 @@
           <t>G | 194呎 (开放式)
 $455万
 $23,432/呎
-(18年-06月-24日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -36915,7 +36915,7 @@
           <t>H | 248呎 (1房)
 $559万
 $22,556/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -36923,7 +36923,7 @@
           <t>J | 249呎 (1房)
 $564万
 $22,632/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -36931,7 +36931,7 @@
           <t>K | 278呎 (1房)
 $621万
 $22,325/呎
-(18年-06月-21日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -36939,7 +36939,7 @@
           <t>L | 193呎 (开放式)
 $469万
 $24,326/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -36954,7 +36954,7 @@
           <t>A | 417呎 (2房)
 $925万
 $22,186/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -36962,7 +36962,7 @@
           <t>B | 251呎 (1房)
 $596万
 $23,759/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -36970,7 +36970,7 @@
           <t>C | 252呎 (1房)
 $585万
 $23,230/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -36978,7 +36978,7 @@
           <t>D | 198呎 (开放式)
 $495万
 $25,013/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -36986,7 +36986,7 @@
           <t>E | 308呎 (1房)
 $719万
 $23,342/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -36994,7 +36994,7 @@
           <t>F | 253呎 (1房)
 $583万
 $23,040/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -37002,7 +37002,7 @@
           <t>G | 194呎 (开放式)
 $456万
 $23,510/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -37010,7 +37010,7 @@
           <t>H | 249呎 (1房)
 $550万
 $22,071/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -37018,7 +37018,7 @@
           <t>J | 249呎 (1房)
 $565万
 $22,701/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -37026,7 +37026,7 @@
           <t>K | 278呎 (1房)
 $636万
 $22,861/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -37034,7 +37034,7 @@
           <t>L | 193呎 (开放式)
 $459万
 $23,794/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -37049,7 +37049,7 @@
           <t>A | 417呎 (2房)
 $941万
 $22,566/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -37057,7 +37057,7 @@
           <t>B | 251呎 (1房)
 $594万
 $23,671/呎
-(18年-06月-25日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -37065,7 +37065,7 @@
           <t>C | 252呎 (1房)
 $595万
 $23,629/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -37073,7 +37073,7 @@
           <t>D | 198呎 (开放式)
 $488万
 $24,657/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -37081,7 +37081,7 @@
           <t>E | 308呎 (1房)
 $709万
 $23,010/呎
-(18年-06月-27日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -37089,7 +37089,7 @@
           <t>F | 253呎 (1房)
 $581万
 $22,961/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -37097,7 +37097,7 @@
           <t>G | 194呎 (开放式)
 $450万
 $23,182/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -37105,7 +37105,7 @@
           <t>H | 248呎 (1房)
 $548万
 $22,080/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -37113,7 +37113,7 @@
           <t>J | 249呎 (1房)
 $575万
 $23,087/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -37121,7 +37121,7 @@
           <t>K | 278呎 (1房)
 $620万
 $22,308/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -37129,7 +37129,7 @@
           <t>L | 193呎 (开放式)
 $458万
 $23,706/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -37144,7 +37144,7 @@
           <t>A | 417呎 (2房)
 $911万
 $21,857/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -37152,7 +37152,7 @@
           <t>B | 251呎 (1房)
 $584万
 $23,254/呎
-(18年-06月-24日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37160,7 +37160,7 @@
           <t>C | 252呎 (1房)
 $573万
 $22,740/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -37168,7 +37168,7 @@
           <t>D | 198呎 (开放式)
 $490万
 $24,727/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -37176,7 +37176,7 @@
           <t>E | 308呎 (1房)
 $711万
 $23,077/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -37184,7 +37184,7 @@
           <t>F | 253呎 (1房)
 $577万
 $22,800/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -37192,7 +37192,7 @@
           <t>G | 194呎 (开放式)
 $446万
 $23,015/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -37200,7 +37200,7 @@
           <t>H | 249呎 (1房)
 $588万
 $23,609/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -37208,7 +37208,7 @@
           <t>J | 249呎 (1房)
 $553万
 $22,216/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -37216,7 +37216,7 @@
           <t>K | 278呎 (1房)
 $646万
 $23,248/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -37224,7 +37224,7 @@
           <t>L | 193呎 (开放式)
 $496万
 $25,716/呎
-(18年-07月-17日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -37239,7 +37239,7 @@
           <t>A | 417呎 (2房)
 $920万
 $22,061/呎
-(18年-07月-09日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -37247,7 +37247,7 @@
           <t>B | 251呎 (1房)
 $595万
 $23,719/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37255,7 +37255,7 @@
           <t>C | 252呎 (1房)
 $567万
 $22,491/呎
-(18年-07月-08日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -37263,7 +37263,7 @@
           <t>D | 198呎 (开放式)
 $479万
 $24,196/呎
-(18年-06月-28日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -37271,7 +37271,7 @@
           <t>E | 308呎 (1房)
 $717万
 $23,285/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -37279,7 +37279,7 @@
           <t>F | 253呎 (1房)
 $578万
 $22,839/呎
-(18年-07月-03日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -37287,7 +37287,7 @@
           <t>G | 194呎 (开放式)
 $442万
 $22,771/呎
-(18年-06月-08日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -37295,7 +37295,7 @@
           <t>H | 249呎 (1房)
 $587万
 $23,591/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -37303,7 +37303,7 @@
           <t>J | 248呎 (1房)
 $548万
 $22,091/呎
-(18年-07月-02日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -37311,7 +37311,7 @@
           <t>K | 278呎 (1房)
 $646万
 $23,226/呎
-(18年-07月-05日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -37319,7 +37319,7 @@
           <t>L | 193呎 (开放式)
 $491万
 $25,428/呎
-(18年-07月-10日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -37334,7 +37334,7 @@
           <t>A | 379呎 (2房)
 $1170万
 $30,872/呎
-(19年-11月-03日)</t>
+(19年-11月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -37342,7 +37342,7 @@
           <t>B | 230呎 (1房)
 $700万
 $30,451/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -37350,7 +37350,7 @@
           <t>C | 230呎 (1房)
 $721万
 $31,359/呎
-(21年-08月-19日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -37358,7 +37358,7 @@
           <t>D | 175呎 (开放式)
 $398万
 $22,743/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -37366,7 +37366,7 @@
           <t>E | 286呎 (1房)
 $700万
 $24,476/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -37374,7 +37374,7 @@
           <t>F | 233呎 (1房)
 $628万
 $26,953/呎
-(23年-03月-15日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -37382,7 +37382,7 @@
           <t>G | 171呎 (开放式)
 $450万
 $26,316/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -37390,7 +37390,7 @@
           <t>H | 227呎 (1房)
 $693万
 $30,521/呎
-(21年-09月-16日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -37398,7 +37398,7 @@
           <t>J | 227呎 (1房)
 $716万
 $31,522/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -37406,7 +37406,7 @@
           <t>K | 257呎 (1房)
 $720万
 $28,016/呎
-(23年-04月-20日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -37414,7 +37414,7 @@
           <t>L | 171呎 (开放式)
 $380万
 $22,222/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-旺角-利奥坊．凯岸.xlsx
+++ b/files/九龙-旺角-利奥坊．凯岸.xlsx
@@ -32810,7 +32810,7 @@
           <t>B | 508呎 (3房)
 $1708万
 $33,622/呎
-(22年-09月)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -32818,7 +32818,7 @@
           <t>C | 509呎 (3房)
 $1300万
 $25,540/呎
-(24年-06月)</t>
+(24年-06月-18日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -32826,7 +32826,7 @@
           <t>D | 579呎 (3房)
 $1388万
 $23,972/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -32848,7 +32848,7 @@
           <t>A | 417呎 (2房)
 $1079万
 $25,877/呎
-(23年-07月)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -32856,7 +32856,7 @@
           <t>B | 251呎 (1房)
 $736万
 $29,341/呎
-(21年-08月)</t>
+(21年-08月-08日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -32864,7 +32864,7 @@
           <t>C | 252呎 (1房)
 $746万
 $29,589/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -32872,7 +32872,7 @@
           <t>D | 198呎 (开放式)
 $638万
 $32,227/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -32880,7 +32880,7 @@
           <t>E | 309呎 (1房)
 $801万
 $25,934/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -32888,7 +32888,7 @@
           <t>F | 253呎 (1房)
 $705万
 $27,861/呎
-(21年-11月)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -32896,7 +32896,7 @@
           <t>G | 194呎 (开放式)
 $448万
 $23,088/呎
-(23年-09月)</t>
+(23年-09月-28日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -32904,7 +32904,7 @@
           <t>H | 249呎 (1房)
 $698万
 $28,012/呎
-(21年-11月)</t>
+(21年-11月-29日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -32912,7 +32912,7 @@
           <t>J | 249呎 (1房)
 $693万
 $27,849/呎
-(21年-11月)</t>
+(21年-11月-29日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -32920,7 +32920,7 @@
           <t>K | 278呎 (1房)
 $576万
 $20,730/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -32928,7 +32928,7 @@
           <t>L | 193呎 (开放式)
 $605万
 $31,332/呎
-(21年-10月)</t>
+(21年-10月-27日)</t>
         </is>
       </c>
     </row>
@@ -32943,7 +32943,7 @@
           <t>A | 417呎 (2房)
 $986万
 $23,646/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -32951,7 +32951,7 @@
           <t>B | 251呎 (1房)
 $727万
 $28,983/呎
-(21年-08月)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -32959,7 +32959,7 @@
           <t>C | 252呎 (1房)
 $745万
 $29,557/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -32967,7 +32967,7 @@
           <t>D | 198呎 (开放式)
 $637万
 $32,181/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -32975,7 +32975,7 @@
           <t>E | 309呎 (1房)
 $899万
 $29,091/呎
-(21年-11月)</t>
+(21年-11月-12日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -32983,7 +32983,7 @@
           <t>F | 253呎 (1房)
 $696万
 $27,523/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -32991,7 +32991,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $25,019/呎
-(23年-04月)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -32999,7 +32999,7 @@
           <t>H | 249呎 (1房)
 $696万
 $27,969/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -33007,7 +33007,7 @@
           <t>J | 249呎 (1房)
 $692万
 $27,801/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -33015,7 +33015,7 @@
           <t>K | 278呎 (1房)
 $569万
 $20,471/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -33023,7 +33023,7 @@
           <t>L | 193呎 (开放式)
 $597万
 $30,936/呎
-(21年-11月)</t>
+(21年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -33038,7 +33038,7 @@
           <t>A | 417呎 (2房)
 $1173万
 $28,122/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -33046,7 +33046,7 @@
           <t>B | 251呎 (1房)
 $722万
 $28,773/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -33054,7 +33054,7 @@
           <t>C | 252呎 (1房)
 $724万
 $28,738/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -33062,7 +33062,7 @@
           <t>D | 198呎 (开放式)
 $643万
 $32,475/呎
-(18年-08月)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -33070,7 +33070,7 @@
           <t>E | 309呎 (1房)
 $863万
 $27,915/呎
-(21年-09月)</t>
+(21年-09月-13日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -33078,7 +33078,7 @@
           <t>F | 253呎 (1房)
 $704万
 $27,832/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -33086,7 +33086,7 @@
           <t>G | 194呎 (开放式)
 $535万
 $27,589/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -33094,7 +33094,7 @@
           <t>H | 249呎 (1房)
 $685万
 $27,510/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -33102,7 +33102,7 @@
           <t>J | 248呎 (1房)
 $653万
 $26,334/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -33110,7 +33110,7 @@
           <t>K | 278呎 (1房)
 $546万
 $19,630/呎
-(24年-03月)</t>
+(24年-03月-07日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -33118,7 +33118,7 @@
           <t>L | 193呎 (开放式)
 $620万
 $32,118/呎
-(18年-07月)</t>
+(18年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -33133,7 +33133,7 @@
           <t>A | 417呎 (2房)
 $1157万
 $27,755/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -33141,7 +33141,7 @@
           <t>B | 251呎 (1房)
 $713万
 $28,398/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -33149,7 +33149,7 @@
           <t>C | 252呎 (1房)
 $730万
 $28,961/呎
-(18年-07月)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -33157,7 +33157,7 @@
           <t>D | 198呎 (开放式)
 $597万
 $30,127/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -33165,7 +33165,7 @@
           <t>E | 309呎 (1房)
 $861万
 $27,860/呎
-(21年-12月)</t>
+(21年-12月-16日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -33173,7 +33173,7 @@
           <t>F | 253呎 (1房)
 $714万
 $28,230/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -33181,7 +33181,7 @@
           <t>G | 194呎 (开放式)
 $537万
 $27,701/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -33189,7 +33189,7 @@
           <t>H | 249呎 (1房)
 $653万
 $26,236/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -33197,7 +33197,7 @@
           <t>J | 249呎 (1房)
 $649万
 $26,051/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -33205,7 +33205,7 @@
           <t>K | 278呎 (1房)
 $533万
 $19,186/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -33213,7 +33213,7 @@
           <t>L | 193呎 (开放式)
 $616万
 $31,904/呎
-(18年-07月)</t>
+(18年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -33228,7 +33228,7 @@
           <t>A | 417呎 (2房)
 $1154万
 $27,679/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -33236,7 +33236,7 @@
           <t>B | 251呎 (1房)
 $703万
 $28,024/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -33244,7 +33244,7 @@
           <t>C | 252呎 (1房)
 $705万
 $27,995/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -33252,7 +33252,7 @@
           <t>D | 198呎 (开放式)
 $595万
 $30,058/呎
-(21年-10月)</t>
+(21年-10月-16日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -33260,7 +33260,7 @@
           <t>E | 309呎 (1房)
 $849万
 $27,491/呎
-(22年-02月)</t>
+(22年-02月-24日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -33268,7 +33268,7 @@
           <t>F | 253呎 (1房)
 $688万
 $27,193/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -33276,7 +33276,7 @@
           <t>G | 194呎 (开放式)
 $534万
 $27,523/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -33284,7 +33284,7 @@
           <t>H | 249呎 (1房)
 $642万
 $25,787/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -33292,7 +33292,7 @@
           <t>J | 249呎 (1房)
 $638万
 $25,604/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -33300,7 +33300,7 @@
           <t>K | 278呎 (1房)
 $530万
 $19,059/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -33308,7 +33308,7 @@
           <t>L | 193呎 (开放式)
 $612万
 $31,695/呎
-(18年-07月)</t>
+(18年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -33323,7 +33323,7 @@
           <t>A | 417呎 (2房)
 $1161万
 $27,835/呎
-(18年-07月)</t>
+(18年-07月-25日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -33331,7 +33331,7 @@
           <t>B | 251呎 (1房)
 $687万
 $27,357/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -33339,7 +33339,7 @@
           <t>C | 252呎 (1房)
 $711万
 $28,207/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -33347,7 +33347,7 @@
           <t>D | 198呎 (开放式)
 $587万
 $29,653/呎
-(21年-10月)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -33355,7 +33355,7 @@
           <t>E | 309呎 (1房)
 $829万
 $26,831/呎
-(22年-05月)</t>
+(22年-05月-11日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -33363,7 +33363,7 @@
           <t>F | 253呎 (1房)
 $691万
 $27,297/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -33371,7 +33371,7 @@
           <t>G | 194呎 (开放式)
 $525万
 $27,060/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -33379,7 +33379,7 @@
           <t>H | 249呎 (1房)
 $638万
 $25,612/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -33387,7 +33387,7 @@
           <t>J | 249呎 (1房)
 $633万
 $25,433/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -33395,7 +33395,7 @@
           <t>K | 278呎 (1房)
 $526万
 $18,929/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -33403,7 +33403,7 @@
           <t>L | 193呎 (开放式)
 $601万
 $31,153/呎
-(18年-07月)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -33418,7 +33418,7 @@
           <t>A | 417呎 (2房)
 $1165万
 $27,934/呎
-(18年-07月)</t>
+(18年-07月-25日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -33426,7 +33426,7 @@
           <t>B | 251呎 (1房)
 $689万
 $27,454/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -33434,7 +33434,7 @@
           <t>C | 252呎 (1房)
 $691万
 $27,437/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -33442,7 +33442,7 @@
           <t>D | 198呎 (开放式)
 $493万
 $24,920/呎
-(23年-06月)</t>
+(23年-06月-04日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -33450,7 +33450,7 @@
           <t>E | 309呎 (1房)
 $725万
 $23,464/呎
-(22年-12月)</t>
+(22年-12月-21日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -33458,7 +33458,7 @@
           <t>F | 253呎 (1房)
 $679万
 $26,837/呎
-(18年-06月)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -33466,7 +33466,7 @@
           <t>G | 194呎 (开放式)
 $521万
 $26,879/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -33474,7 +33474,7 @@
           <t>H | 249呎 (1房)
 $653万
 $26,244/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -33482,7 +33482,7 @@
           <t>J | 249呎 (1房)
 $629万
 $25,257/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -33490,7 +33490,7 @@
           <t>K | 278呎 (1房)
 $617万
 $22,193/呎
-(23年-09月)</t>
+(23年-09月-13日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -33498,7 +33498,7 @@
           <t>L | 193呎 (开放式)
 $597万
 $30,946/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -33513,7 +33513,7 @@
           <t>A | 417呎 (2房)
 $1123万
 $26,935/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -33521,7 +33521,7 @@
           <t>B | 251呎 (1房)
 $684万
 $27,270/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -33529,7 +33529,7 @@
           <t>C | 252呎 (1房)
 $687万
 $27,252/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -33537,7 +33537,7 @@
           <t>D | 198呎 (开放式)
 $611万
 $30,861/呎
-(18年-10月)</t>
+(18年-10月-22日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -33545,7 +33545,7 @@
           <t>E | 309呎 (1房)
 $818万
 $26,467/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -33553,7 +33553,7 @@
           <t>F | 253呎 (1房)
 $682万
 $26,941/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -33561,7 +33561,7 @@
           <t>G | 194呎 (开放式)
 $518万
 $26,698/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -33569,7 +33569,7 @@
           <t>H | 249呎 (1房)
 $629万
 $25,268/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -33577,7 +33577,7 @@
           <t>J | 249呎 (1房)
 $631万
 $25,349/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -33585,7 +33585,7 @@
           <t>K | 278呎 (1房)
 $613万
 $22,043/呎
-(23年-08月)</t>
+(23年-08月-30日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -33593,7 +33593,7 @@
           <t>L | 193呎 (开放式)
 $576万
 $29,839/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -33608,7 +33608,7 @@
           <t>A | 417呎 (2房)
 $1116万
 $26,751/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -33616,7 +33616,7 @@
           <t>B | 251呎 (1房)
 $694万
 $27,643/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -33624,7 +33624,7 @@
           <t>C | 252呎 (1房)
 $689万
 $27,352/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -33632,7 +33632,7 @@
           <t>D | 198呎 (开放式)
 $607万
 $30,642/呎
-(19年-08月)</t>
+(19年-08月-15日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -33640,7 +33640,7 @@
           <t>E | 309呎 (1房)
 $866万
 $28,042/呎
-(18年-09月)</t>
+(18年-09月-05日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -33648,7 +33648,7 @@
           <t>F | 253呎 (1房)
 $677万
 $26,762/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -33656,7 +33656,7 @@
           <t>G | 194呎 (开放式)
 $515万
 $26,522/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -33664,7 +33664,7 @@
           <t>H | 249呎 (1房)
 $631万
 $25,357/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -33672,7 +33672,7 @@
           <t>J | 249呎 (1房)
 $620万
 $24,910/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -33680,7 +33680,7 @@
           <t>K | 278呎 (1房)
 $600万
 $21,588/呎
-(23年-11月)</t>
+(23年-11月-13日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -33688,7 +33688,7 @@
           <t>L | 193呎 (开放式)
 $589万
 $30,518/呎
-(18年-07月)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -33703,7 +33703,7 @@
           <t>A | 417呎 (2房)
 $1108万
 $26,565/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -33711,7 +33711,7 @@
           <t>B | 251呎 (1房)
 $675万
 $26,891/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -33719,7 +33719,7 @@
           <t>C | 252呎 (1房)
 $692万
 $27,449/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -33727,7 +33727,7 @@
           <t>D | 198呎 (开放式)
 $427万
 $21,554/呎
-(23年-10月)</t>
+(23年-10月-29日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -33735,7 +33735,7 @@
           <t>E | 309呎 (1房)
 $835万
 $27,038/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -33743,7 +33743,7 @@
           <t>F | 253呎 (1房)
 $687万
 $27,142/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -33751,7 +33751,7 @@
           <t>G | 194呎 (开放式)
 $516万
 $26,618/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -33759,7 +33759,7 @@
           <t>H | 249呎 (1房)
 $1751万
 $70,317/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -33767,7 +33767,7 @@
           <t>J | 249呎 (1房)
 $622万
 $24,999/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -33775,7 +33775,7 @@
           <t>K | 278呎 (1房)
 $663万
 $23,856/呎
-(23年-07月)</t>
+(23年-07月-30日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -33783,7 +33783,7 @@
           <t>L | 193呎 (开放式)
 $586万
 $30,355/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -33798,7 +33798,7 @@
           <t>A | 417呎 (2房)
 $1100万
 $26,380/呎
-(18年-07月)</t>
+(18年-07月-15日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -33806,7 +33806,7 @@
           <t>B | 251呎 (1房)
 $670万
 $26,708/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -33814,7 +33814,7 @@
           <t>C | 252呎 (1房)
 $680万
 $26,979/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -33822,7 +33822,7 @@
           <t>D | 198呎 (开放式)
 $455万
 $22,980/呎
-(23年-08月)</t>
+(23年-08月-30日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -33830,7 +33830,7 @@
           <t>E | 311呎 (1房)
 $821万
 $26,398/呎
-(18年-06月)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -33838,7 +33838,7 @@
           <t>F | 253呎 (1房)
 $661万
 $26,131/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -33846,7 +33846,7 @@
           <t>G | 194呎 (开放式)
 $508万
 $26,184/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -33854,7 +33854,7 @@
           <t>H | 249呎 (1房)
 $636万
 $25,527/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -33862,7 +33862,7 @@
           <t>J | 249呎 (1房)
 $612万
 $24,563/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -33870,7 +33870,7 @@
           <t>K | 278呎 (1房)
 $642万
 $23,094/呎
-(23年-04月)</t>
+(23年-04月-10日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -33878,7 +33878,7 @@
           <t>L | 193呎 (开放式)
 $570万
 $29,531/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -33893,7 +33893,7 @@
           <t>A | 417呎 (2房)
 $1092万
 $26,196/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -33901,7 +33901,7 @@
           <t>B | 251呎 (1房)
 $666万
 $26,517/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -33909,7 +33909,7 @@
           <t>C | 252呎 (1房)
 $675万
 $26,796/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -33917,7 +33917,7 @@
           <t>D | 198呎 (开放式)
 $588万
 $29,690/呎
-(18年-08月)</t>
+(18年-08月-27日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -33925,7 +33925,7 @@
           <t>E | 311呎 (1房)
 $815万
 $26,218/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -33933,7 +33933,7 @@
           <t>F | 253呎 (1房)
 $677万
 $26,778/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -33941,7 +33941,7 @@
           <t>G | 194呎 (开放式)
 $504万
 $25,993/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -33949,7 +33949,7 @@
           <t>H | 249呎 (1房)
 $631万
 $25,346/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -33957,7 +33957,7 @@
           <t>J | 249呎 (1房)
 $614万
 $24,648/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -33965,7 +33965,7 @@
           <t>K | 278呎 (1房)
 $638万
 $22,934/呎
-(23年-04月)</t>
+(23年-04月-13日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -33973,7 +33973,7 @@
           <t>L | 193呎 (开放式)
 $566万
 $29,327/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -33988,7 +33988,7 @@
           <t>A | 417呎 (2房)
 $1085万
 $26,010/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -33996,7 +33996,7 @@
           <t>B | 251呎 (1房)
 $663万
 $26,425/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -34004,7 +34004,7 @@
           <t>C | 252呎 (1房)
 $673万
 $26,697/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -34012,7 +34012,7 @@
           <t>D | 197呎 (开放式)
 $586万
 $29,739/呎
-(18年-08月)</t>
+(18年-08月-23日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -34020,7 +34020,7 @@
           <t>E | 309呎 (1房)
 $818万
 $26,476/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>F | 253呎 (1房)
 $661万
 $26,140/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -34036,7 +34036,7 @@
           <t>G | 194呎 (开放式)
 $502万
 $25,900/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -34044,7 +34044,7 @@
           <t>H | 249呎 (1房)
 $616万
 $24,744/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -34052,7 +34052,7 @@
           <t>J | 249呎 (1房)
 $605万
 $24,303/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -34060,7 +34060,7 @@
           <t>K | 278呎 (1房)
 $635万
 $22,853/呎
-(23年-08月)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -34068,7 +34068,7 @@
           <t>L | 193呎 (开放式)
 $562万
 $29,118/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -34083,7 +34083,7 @@
           <t>A | 417呎 (2房)
 $1069万
 $25,639/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -34091,7 +34091,7 @@
           <t>B | 251呎 (1房)
 $658万
 $26,234/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -34099,7 +34099,7 @@
           <t>C | 252呎 (1房)
 $668万
 $26,507/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -34107,7 +34107,7 @@
           <t>D | 198呎 (开放式)
 $447万
 $22,574/呎
-(23年-09月)</t>
+(23年-09月-27日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -34115,7 +34115,7 @@
           <t>E | 311呎 (1房)
 $806万
 $25,929/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -34123,7 +34123,7 @@
           <t>F | 253呎 (1房)
 $657万
 $25,966/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -34131,7 +34131,7 @@
           <t>G | 194呎 (开放式)
 $504万
 $25,989/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -34139,7 +34139,7 @@
           <t>H | 249呎 (1房)
 $612万
 $24,567/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -34147,7 +34147,7 @@
           <t>J | 248呎 (1房)
 $620万
 $24,994/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -34155,7 +34155,7 @@
           <t>K | 278呎 (1房)
 $639万
 $22,987/呎
-(23年-05月)</t>
+(23年-05月-14日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -34163,7 +34163,7 @@
           <t>L | 193呎 (开放式)
 $544万
 $28,205/呎
-(18年-06月)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34178,7 @@
           <t>A | 417呎 (2房)
 $1663万
 $39,889/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -34186,7 +34186,7 @@
           <t>B | 251呎 (1房)
 $654万
 $26,046/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -34194,7 +34194,7 @@
           <t>C | 252呎 (1房)
 $656万
 $26,050/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -34202,7 +34202,7 @@
           <t>D | 198呎 (开放式)
 $438万
 $22,102/呎
-(23年-09月)</t>
+(23年-09月-03日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -34210,7 +34210,7 @@
           <t>E | 311呎 (1房)
 $795万
 $25,559/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -34218,7 +34218,7 @@
           <t>F | 253呎 (1房)
 $680万
 $26,858/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -34226,7 +34226,7 @@
           <t>G | 194呎 (开放式)
 $495万
 $25,537/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -34234,7 +34234,7 @@
           <t>H | 249呎 (1房)
 $607万
 $24,393/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -34242,7 +34242,7 @@
           <t>J | 249呎 (1房)
 $596万
 $23,952/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -34250,7 +34250,7 @@
           <t>K | 278呎 (1房)
 $626万
 $22,532/呎
-(23年-05月)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -34258,7 +34258,7 @@
           <t>L | 193呎 (开放式)
 $538万
 $27,885/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -34273,7 +34273,7 @@
           <t>A | 417呎 (2房)
 $1035万
 $24,823/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -34281,7 +34281,7 @@
           <t>B | 251呎 (1房)
 $649万
 $25,863/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -34289,7 +34289,7 @@
           <t>C | 252呎 (1房)
 $665万
 $26,406/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -34297,7 +34297,7 @@
           <t>D | 198呎 (开放式)
 $573万
 $28,956/呎
-(18年-09月)</t>
+(18年-09月-03日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -34305,7 +34305,7 @@
           <t>E | 311呎 (1房)
 $789万
 $25,371/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -34313,7 +34313,7 @@
           <t>F | 253呎 (1房)
 $648万
 $25,609/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -34321,7 +34321,7 @@
           <t>G | 194呎 (开放式)
 $492万
 $25,361/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -34329,7 +34329,7 @@
           <t>H | 249呎 (1房)
 $645万
 $25,890/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -34337,7 +34337,7 @@
           <t>J | 249呎 (1房)
 $598万
 $24,031/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -34345,7 +34345,7 @@
           <t>K | 278呎 (1房)
 $630万
 $22,659/呎
-(23年-04月)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -34353,7 +34353,7 @@
           <t>L | 193呎 (开放式)
 $534万
 $27,681/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34368,7 @@
           <t>A | 417呎 (2房)
 $1028万
 $24,641/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -34376,7 +34376,7 @@
           <t>B | 251呎 (1房)
 $644万
 $25,671/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -34384,7 +34384,7 @@
           <t>C | 252呎 (1房)
 $654万
 $25,947/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -34392,7 +34392,7 @@
           <t>D | 197呎 (开放式)
 $575万
 $29,195/呎
-(18年-08月)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -34400,7 +34400,7 @@
           <t>E | 311呎 (1房)
 $783万
 $25,185/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -34408,7 +34408,7 @@
           <t>F | 253呎 (1房)
 $637万
 $25,166/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -34416,7 +34416,7 @@
           <t>G | 194呎 (开放式)
 $489万
 $25,185/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -34424,7 +34424,7 @@
           <t>H | 249呎 (1房)
 $592万
 $23,792/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -34432,7 +34432,7 @@
           <t>J | 248呎 (1房)
 $588万
 $23,704/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -34440,7 +34440,7 @@
           <t>K | 278呎 (1房)
 $726万
 $26,100/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -34448,7 +34448,7 @@
           <t>L | 193呎 (开放式)
 $525万
 $27,186/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -34463,7 +34463,7 @@
           <t>A | 417呎 (2房)
 $1031万
 $24,714/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -34471,7 +34471,7 @@
           <t>B | 251呎 (1房)
 $652万
 $25,975/呎
-(19年-07月)</t>
+(19年-07月-09日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -34479,7 +34479,7 @@
           <t>C | 252呎 (1房)
 $663万
 $26,301/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -34487,7 +34487,7 @@
           <t>D | 198呎 (开放式)
 $533万
 $26,897/呎
-(18年-07月)</t>
+(18年-07月-15日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -34495,7 +34495,7 @@
           <t>E | 309呎 (1房)
 $769万
 $24,900/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -34503,7 +34503,7 @@
           <t>F | 253呎 (1房)
 $639万
 $25,252/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -34511,7 +34511,7 @@
           <t>G | 194呎 (开放式)
 $511万
 $26,325/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -34519,7 +34519,7 @@
           <t>H | 249呎 (1房)
 $594万
 $23,869/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -34527,7 +34527,7 @@
           <t>J | 249呎 (1房)
 $584万
 $23,437/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -34535,7 +34535,7 @@
           <t>K | 278呎 (1房)
 $720万
 $25,913/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -34543,7 +34543,7 @@
           <t>L | 193呎 (开放式)
 $521万
 $26,984/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -34558,7 +34558,7 @@
           <t>A | 417呎 (2房)
 $1023万
 $24,529/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -34566,7 +34566,7 @@
           <t>B | 251呎 (1房)
 $635万
 $25,297/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -34574,7 +34574,7 @@
           <t>C | 252呎 (1房)
 $644万
 $25,573/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -34582,7 +34582,7 @@
           <t>D | 198呎 (开放式)
 $529万
 $26,701/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -34590,7 +34590,7 @@
           <t>E | 309呎 (1房)
 $772万
 $24,972/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -34598,7 +34598,7 @@
           <t>F | 253呎 (1房)
 $641万
 $25,335/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -34606,7 +34606,7 @@
           <t>G | 194呎 (开放式)
 $492万
 $25,350/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -34614,7 +34614,7 @@
           <t>H | 249呎 (1房)
 $590万
 $23,692/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -34622,7 +34622,7 @@
           <t>J | 249呎 (1房)
 $579万
 $23,258/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -34630,7 +34630,7 @@
           <t>K | 278呎 (1房)
 $708万
 $25,455/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -34638,7 +34638,7 @@
           <t>L | 193呎 (开放式)
 $517万
 $26,777/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -34653,7 +34653,7 @@
           <t>A | 417呎 (2房)
 $1008万
 $24,183/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -34661,7 +34661,7 @@
           <t>B | 251呎 (1房)
 $646万
 $25,726/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -34669,7 +34669,7 @@
           <t>C | 252呎 (1房)
 $635万
 $25,216/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -34677,7 +34677,7 @@
           <t>D | 197呎 (开放式)
 $532万
 $27,016/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -34685,7 +34685,7 @@
           <t>E | 309呎 (1房)
 $785万
 $25,401/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -34693,7 +34693,7 @@
           <t>F | 253呎 (1房)
 $632万
 $24,987/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -34701,7 +34701,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $25,000/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -34709,7 +34709,7 @@
           <t>H | 249呎 (1房)
 $582万
 $23,361/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -34717,7 +34717,7 @@
           <t>J | 248呎 (1房)
 $583万
 $23,512/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -34725,7 +34725,7 @@
           <t>K | 278呎 (1房)
 $713万
 $25,630/呎
-(18年-07月)</t>
+(18年-07月-15日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -34733,7 +34733,7 @@
           <t>L | 193呎 (开放式)
 $515万
 $26,674/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -34748,7 +34748,7 @@
           <t>A | 417呎 (2房)
 $762万
 $18,264/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -34756,7 +34756,7 @@
           <t>B | 251呎 (1房)
 $628万
 $25,014/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -34764,7 +34764,7 @@
           <t>C | 252呎 (1房)
 $637万
 $25,291/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -34772,7 +34772,7 @@
           <t>D | 198呎 (开放式)
 $528万
 $26,681/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -34780,7 +34780,7 @@
           <t>E | 311呎 (1房)
 $763万
 $24,534/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -34788,7 +34788,7 @@
           <t>F | 253呎 (1房)
 $621万
 $24,546/呎
-(18年-06月)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -34796,7 +34796,7 @@
           <t>G | 194呎 (开放式)
 $482万
 $24,821/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -34804,7 +34804,7 @@
           <t>H | 248呎 (1房)
 $583万
 $23,524/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -34812,7 +34812,7 @@
           <t>J | 249呎 (1房)
 $573万
 $23,002/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -34820,7 +34820,7 @@
           <t>K | 278呎 (1房)
 $707万
 $25,440/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -34828,7 +34828,7 @@
           <t>L | 193呎 (开放式)
 $553万
 $28,661/呎
-(18年-07月)</t>
+(18年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -34843,7 +34843,7 @@
           <t>A | 417呎 (2房)
 $1129万
 $27,085/呎
-(18年-09月)</t>
+(18年-09月-11日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -34851,7 +34851,7 @@
           <t>B | 251呎 (1房)
 $621万
 $24,734/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -34859,7 +34859,7 @@
           <t>C | 252呎 (1房)
 $630万
 $25,013/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -34867,7 +34867,7 @@
           <t>D | 198呎 (开放式)
 $522万
 $26,376/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -34875,7 +34875,7 @@
           <t>E | 309呎 (1房)
 $754万
 $24,410/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -34883,7 +34883,7 @@
           <t>F | 253呎 (1房)
 $621万
 $24,539/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -34891,7 +34891,7 @@
           <t>G | 194呎 (开放式)
 $476万
 $24,544/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -34899,7 +34899,7 @@
           <t>H | 249呎 (1房)
 $645万
 $25,897/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -34907,7 +34907,7 @@
           <t>J | 249呎 (1房)
 $566万
 $22,739/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -34915,7 +34915,7 @@
           <t>K | 278呎 (1房)
 $699万
 $25,157/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -34923,7 +34923,7 @@
           <t>L | 193呎 (开放式)
 $499万
 $25,847/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -34938,7 +34938,7 @@
           <t>A | 379呎 (2房)
 $788万
 $20,792/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -34946,7 +34946,7 @@
           <t>B | 229呎 (1房)
 $721万
 $31,480/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -34954,7 +34954,7 @@
           <t>C | 230呎 (1房)
 $740万
 $32,167/呎
-(22年-01月)</t>
+(22年-01月-17日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -34962,7 +34962,7 @@
           <t>D | 175呎 (开放式)
 $480万
 $27,429/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -34970,7 +34970,7 @@
           <t>E | 290呎 (1房)
 $680万
 $23,448/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -34978,7 +34978,7 @@
           <t>F | 233呎 (1房)
 $610万
 $26,180/呎
-(23年-07月)</t>
+(23年-07月-02日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -34986,7 +34986,7 @@
           <t>G | 171呎 (开放式)
 $596万
 $34,837/呎
-(22年-09月)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -34994,7 +34994,7 @@
           <t>H | 227呎 (1房)
 $681万
 $30,005/呎
-(21年-06月)</t>
+(21年-06月-08日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -35002,7 +35002,7 @@
           <t>J | 227呎 (1房)
 $693万
 $30,511/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -35010,7 +35010,7 @@
           <t>K | 257呎 (1房)
 $635万
 $24,708/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -35018,7 +35018,7 @@
           <t>L | 171呎 (开放式)
 $618万
 $36,123/呎
-(22年-07月)</t>
+(22年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -35198,7 +35198,7 @@
           <t>A | 632呎 (3房)
 $2000万
 $31,646/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -35206,7 +35206,7 @@
           <t>B | 506呎 (3房)
 $1689万
 $33,375/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -35222,7 +35222,7 @@
           <t>D | 579呎 (3房)
 $1660万
 $28,670/呎
-(22年-10月)</t>
+(22年-10月-30日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -35244,7 +35244,7 @@
           <t>A | 417呎 (2房)
 $951万
 $22,803/呎
-(23年-12月)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -35252,7 +35252,7 @@
           <t>B | 251呎 (1房)
 $740万
 $29,496/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -35260,7 +35260,7 @@
           <t>C | 252呎 (1房)
 $739万
 $29,341/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -35268,7 +35268,7 @@
           <t>D | 198呎 (开放式)
 $637万
 $32,160/呎
-(18年-09月)</t>
+(18年-09月-05日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -35276,7 +35276,7 @@
           <t>E | 307呎 (1房)
 $766万
 $24,964/呎
-(23年-04月)</t>
+(23年-04月-10日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -35284,7 +35284,7 @@
           <t>F | 253呎 (1房)
 $702万
 $27,747/呎
-(21年-11月)</t>
+(21年-11月-15日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -35292,7 +35292,7 @@
           <t>G | 194呎 (开放式)
 $550万
 $28,336/呎
-(21年-11月)</t>
+(21年-11月-29日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -35300,7 +35300,7 @@
           <t>H | 249呎 (1房)
 $708万
 $28,449/呎
-(21年-12月)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -35308,7 +35308,7 @@
           <t>J | 249呎 (1房)
 $751万
 $30,144/呎
-(18年-09月)</t>
+(18年-09月-27日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -35316,7 +35316,7 @@
           <t>K | 278呎 (1房)
 $776万
 $27,926/呎
-(22年-04月)</t>
+(22年-04月-25日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -35324,7 +35324,7 @@
           <t>L | 193呎 (开放式)
 $383万
 $19,835/呎
-(25年-08月)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -35339,7 +35339,7 @@
           <t>A | 417呎 (2房)
 $1233万
 $29,575/呎
-(19年-05月)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -35347,7 +35347,7 @@
           <t>B | 251呎 (1房)
 $724万
 $28,829/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -35355,7 +35355,7 @@
           <t>C | 252呎 (1房)
 $738万
 $29,291/呎
-(18年-07月)</t>
+(18年-07月-12日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -35363,7 +35363,7 @@
           <t>D | 198呎 (开放式)
 $629万
 $31,758/呎
-(18年-08月)</t>
+(18年-08月-16日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -35371,7 +35371,7 @@
           <t>E | 307呎 (1房)
 $885万
 $28,815/呎
-(21年-09月)</t>
+(21年-09月-02日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -35379,7 +35379,7 @@
           <t>F | 253呎 (1房)
 $701万
 $27,714/呎
-(21年-11月)</t>
+(21年-11月-03日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -35387,7 +35387,7 @@
           <t>G | 194呎 (开放式)
 $543万
 $27,993/呎
-(21年-12月)</t>
+(21年-12月-01日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -35395,7 +35395,7 @@
           <t>H | 249呎 (1房)
 $707万
 $28,411/呎
-(21年-11月)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -35403,7 +35403,7 @@
           <t>J | 249呎 (1房)
 $726万
 $29,162/呎
-(18年-09月)</t>
+(18年-09月-13日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -35411,7 +35411,7 @@
           <t>K | 278呎 (1房)
 $767万
 $27,573/呎
-(22年-03月)</t>
+(22年-03月-01日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -35419,7 +35419,7 @@
           <t>L | 193呎 (开放式)
 $425万
 $22,002/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -35434,7 +35434,7 @@
           <t>A | 417呎 (2房)
 $1127万
 $27,034/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -35442,7 +35442,7 @@
           <t>B | 251呎 (1房)
 $695万
 $27,679/呎
-(18年-07月)</t>
+(18年-07月-24日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -35450,7 +35450,7 @@
           <t>C | 252呎 (1房)
 $709万
 $28,133/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -35458,7 +35458,7 @@
           <t>D | 198呎 (开放式)
 $597万
 $30,141/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -35466,7 +35466,7 @@
           <t>E | 307呎 (1房)
 $848万
 $27,633/呎
-(21年-10月)</t>
+(21年-10月-21日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -35474,7 +35474,7 @@
           <t>F | 253呎 (1房)
 $647万
 $25,556/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -35482,7 +35482,7 @@
           <t>G | 194呎 (开放式)
 $517万
 $26,637/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -35490,7 +35490,7 @@
           <t>H | 249呎 (1房)
 $618万
 $24,817/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -35498,7 +35498,7 @@
           <t>J | 249呎 (1房)
 $647万
 $26,003/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -35506,7 +35506,7 @@
           <t>K | 278呎 (1房)
 $784万
 $28,203/呎
-(18年-08月)</t>
+(18年-08月-15日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -35514,7 +35514,7 @@
           <t>L | 193呎 (开放式)
 $527万
 $27,319/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35529,7 @@
           <t>A | 417呎 (2房)
 $1134万
 $27,199/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -35537,7 +35537,7 @@
           <t>B | 251呎 (1房)
 $660万
 $26,298/呎
-(18年-06月)</t>
+(18年-06月-24日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -35545,7 +35545,7 @@
           <t>C | 252呎 (1房)
 $660万
 $26,179/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -35553,7 +35553,7 @@
           <t>D | 198呎 (开放式)
 $589万
 $29,738/呎
-(18年-06月)</t>
+(18年-06月-30日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -35561,7 +35561,7 @@
           <t>E | 307呎 (1房)
 $884万
 $28,782/呎
-(19年-06月)</t>
+(19年-06月-19日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -35569,7 +35569,7 @@
           <t>F | 253呎 (1房)
 $642万
 $25,395/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -35577,7 +35577,7 @@
           <t>G | 194呎 (开放式)
 $498万
 $25,655/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -35585,7 +35585,7 @@
           <t>H | 249呎 (1房)
 $614万
 $24,655/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -35593,7 +35593,7 @@
           <t>J | 249呎 (1房)
 $630万
 $25,307/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -35601,7 +35601,7 @@
           <t>K | 278呎 (1房)
 $643万
 $23,131/呎
-(23年-03月)</t>
+(23年-03月-08日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -35609,7 +35609,7 @@
           <t>L | 193呎 (开放式)
 $524万
 $27,141/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -35624,7 +35624,7 @@
           <t>A | 417呎 (2房)
 $1098万
 $26,334/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -35632,7 +35632,7 @@
           <t>B | 251呎 (1房)
 $645万
 $25,687/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -35640,7 +35640,7 @@
           <t>C | 252呎 (1房)
 $644万
 $25,575/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -35648,7 +35648,7 @@
           <t>D | 198呎 (开放式)
 $553万
 $27,947/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -35656,7 +35656,7 @@
           <t>E | 307呎 (1房)
 $881万
 $28,700/呎
-(18年-08月)</t>
+(18年-08月-21日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -35664,7 +35664,7 @@
           <t>F | 253呎 (1房)
 $645万
 $25,495/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -35672,7 +35672,7 @@
           <t>G | 194呎 (开放式)
 $500万
 $25,762/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -35680,7 +35680,7 @@
           <t>H | 249呎 (1房)
 $610万
 $24,493/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -35688,7 +35688,7 @@
           <t>J | 248呎 (1房)
 $619万
 $24,972/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -35696,7 +35696,7 @@
           <t>K | 278呎 (1房)
 $766万
 $27,543/呎
-(18年-08月)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -35704,7 +35704,7 @@
           <t>L | 193呎 (开放式)
 $526万
 $27,248/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35719,7 @@
           <t>A | 417呎 (2房)
 $1072万
 $25,716/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -35727,7 +35727,7 @@
           <t>B | 251呎 (1房)
 $650万
 $25,878/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -35735,7 +35735,7 @@
           <t>C | 252呎 (1房)
 $643万
 $25,505/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -35743,7 +35743,7 @@
           <t>D | 198呎 (开放式)
 $546万
 $27,568/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -35751,7 +35751,7 @@
           <t>E | 308呎 (1房)
 $869万
 $28,217/呎
-(18年-08月)</t>
+(18年-08月-13日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -35759,7 +35759,7 @@
           <t>F | 253呎 (1房)
 $634万
 $25,068/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -35767,7 +35767,7 @@
           <t>G | 194呎 (开放式)
 $491万
 $25,327/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -35775,7 +35775,7 @@
           <t>H | 249呎 (1房)
 $600万
 $24,078/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -35783,7 +35783,7 @@
           <t>J | 249呎 (1房)
 $615万
 $24,708/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -35791,7 +35791,7 @@
           <t>K | 278呎 (1房)
 $761万
 $27,362/呎
-(18年-07月)</t>
+(18年-07月-26日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -35799,7 +35799,7 @@
           <t>L | 193呎 (开放式)
 $517万
 $26,792/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -35814,7 +35814,7 @@
           <t>A | 417呎 (2房)
 $1065万
 $25,541/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -35822,7 +35822,7 @@
           <t>B | 251呎 (1房)
 $625万
 $24,920/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -35830,7 +35830,7 @@
           <t>C | 252呎 (1房)
 $632万
 $25,073/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -35838,7 +35838,7 @@
           <t>D | 197呎 (开放式)
 $542万
 $27,518/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -35846,7 +35846,7 @@
           <t>E | 308呎 (1房)
 $881万
 $28,608/呎
-(18年-07月)</t>
+(18年-07月-16日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -35854,7 +35854,7 @@
           <t>F | 253呎 (1房)
 $637万
 $25,169/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -35862,7 +35862,7 @@
           <t>G | 194呎 (开放式)
 $488万
 $25,160/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -35870,7 +35870,7 @@
           <t>H | 249呎 (1房)
 $596万
 $23,918/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -35878,7 +35878,7 @@
           <t>J | 249呎 (1房)
 $618万
 $24,802/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -35886,7 +35886,7 @@
           <t>K | 278呎 (1房)
 $727万
 $26,151/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -35894,7 +35894,7 @@
           <t>L | 193呎 (开放式)
 $514万
 $26,615/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35909,7 @@
           <t>A | 417呎 (2房)
 $1069万
 $25,635/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -35917,7 +35917,7 @@
           <t>B | 251呎 (1房)
 $621万
 $24,749/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -35925,7 +35925,7 @@
           <t>C | 252呎 (1房)
 $628万
 $24,907/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -35933,7 +35933,7 @@
           <t>D | 198呎 (开放式)
 $538万
 $27,190/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -35941,7 +35941,7 @@
           <t>E | 308呎 (1房)
 $866万
 $28,124/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -35949,7 +35949,7 @@
           <t>F | 253呎 (1房)
 $633万
 $25,006/呎
-(18年-06月)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -35957,7 +35957,7 @@
           <t>G | 194呎 (开放式)
 $485万
 $24,999/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -35965,7 +35965,7 @@
           <t>H | 249呎 (1房)
 $592万
 $23,758/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -35973,7 +35973,7 @@
           <t>J | 249呎 (1房)
 $607万
 $24,376/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -35981,7 +35981,7 @@
           <t>K | 278呎 (1房)
 $715万
 $25,705/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -35989,7 +35989,7 @@
           <t>L | 193呎 (开放式)
 $516万
 $26,716/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -36004,7 +36004,7 @@
           <t>A | 417呎 (2房)
 $1051万
 $25,194/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -36012,7 +36012,7 @@
           <t>B | 251呎 (1房)
 $617万
 $24,583/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -36020,7 +36020,7 @@
           <t>C | 252呎 (1房)
 $630万
 $25,002/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -36028,7 +36028,7 @@
           <t>D | 197呎 (开放式)
 $529万
 $26,856/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -36036,7 +36036,7 @@
           <t>E | 307呎 (1房)
 $869万
 $28,305/呎
-(18年-08月)</t>
+(18年-08月-20日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -36044,7 +36044,7 @@
           <t>F | 253呎 (1房)
 $622万
 $24,584/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -36052,7 +36052,7 @@
           <t>G | 194呎 (开放式)
 $507万
 $26,139/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -36060,7 +36060,7 @@
           <t>H | 248呎 (1房)
 $594万
 $23,942/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -36068,7 +36068,7 @@
           <t>J | 249呎 (1房)
 $622万
 $24,976/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -36076,7 +36076,7 @@
           <t>K | 278呎 (1房)
 $710万
 $25,527/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -36084,7 +36084,7 @@
           <t>L | 193呎 (开放式)
 $507万
 $26,260/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -36099,7 +36099,7 @@
           <t>A | 417呎 (2房)
 $994万
 $23,834/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -36107,7 +36107,7 @@
           <t>B | 251呎 (1房)
 $619万
 $24,673/呎
-(18年-06月)</t>
+(18年-06月-24日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -36115,7 +36115,7 @@
           <t>C | 252呎 (1房)
 $626万
 $24,830/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -36123,7 +36123,7 @@
           <t>D | 198呎 (开放式)
 $525万
 $26,533/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -36131,7 +36131,7 @@
           <t>E | 308呎 (1房)
 $812万
 $26,366/呎
-(18年-06月)</t>
+(18年-06月-22日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -36139,7 +36139,7 @@
           <t>F | 253呎 (1房)
 $624万
 $24,679/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -36147,7 +36147,7 @@
           <t>G | 194呎 (开放式)
 $484万
 $24,925/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -36155,7 +36155,7 @@
           <t>H | 249呎 (1房)
 $584万
 $23,437/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -36163,7 +36163,7 @@
           <t>J | 248呎 (1房)
 $599万
 $24,141/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -36171,7 +36171,7 @@
           <t>K | 278呎 (1房)
 $712万
 $25,620/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -36179,7 +36179,7 @@
           <t>L | 193呎 (开放式)
 $503万
 $26,083/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -36194,7 +36194,7 @@
           <t>A | 417呎 (2房)
 $977万
 $23,424/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -36202,7 +36202,7 @@
           <t>B | 251呎 (1房)
 $609万
 $24,250/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -36210,7 +36210,7 @@
           <t>C | 252呎 (1房)
 $694万
 $27,543/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -36218,7 +36218,7 @@
           <t>D | 198呎 (开放式)
 $538万
 $27,178/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -36226,7 +36226,7 @@
           <t>E | 307呎 (1房)
 $815万
 $26,542/呎
-(18年-07月)</t>
+(18年-07月-18日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -36234,7 +36234,7 @@
           <t>F | 253呎 (1房)
 $620万
 $24,512/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -36242,7 +36242,7 @@
           <t>G | 194呎 (开放式)
 $490万
 $25,278/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -36250,7 +36250,7 @@
           <t>H | 249呎 (1房)
 $580万
 $23,273/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -36258,7 +36258,7 @@
           <t>J | 249呎 (1房)
 $601万
 $24,127/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -36266,7 +36266,7 @@
           <t>K | 278呎 (1房)
 $667万
 $23,983/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -36274,7 +36274,7 @@
           <t>L | 193呎 (开放式)
 $500万
 $25,911/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -36289,7 +36289,7 @@
           <t>A | 417呎 (2房)
 $1001万
 $23,995/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -36297,7 +36297,7 @@
           <t>B | 251呎 (1房)
 $611万
 $24,337/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -36305,7 +36305,7 @@
           <t>C | 252呎 (1房)
 $611万
 $24,240/呎
-(18年-06月)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -36313,7 +36313,7 @@
           <t>D | 198呎 (开放式)
 $523万
 $26,434/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -36321,7 +36321,7 @@
           <t>E | 307呎 (1房)
 $809万
 $26,358/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -36329,7 +36329,7 @@
           <t>F | 253呎 (1房)
 $610万
 $24,099/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -36337,7 +36337,7 @@
           <t>G | 194呎 (开放式)
 $472万
 $24,338/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -36345,7 +36345,7 @@
           <t>H | 249呎 (1房)
 $576万
 $23,113/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -36353,7 +36353,7 @@
           <t>J | 249呎 (1房)
 $590万
 $23,712/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -36361,7 +36361,7 @@
           <t>K | 278呎 (1房)
 $662万
 $23,814/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -36369,7 +36369,7 @@
           <t>L | 193呎 (开放式)
 $502万
 $26,005/呎
-(18年-07月)</t>
+(18年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -36384,7 +36384,7 @@
           <t>A | 417呎 (2房)
 $973万
 $23,339/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -36392,7 +36392,7 @@
           <t>B | 251呎 (1房)
 $639万
 $25,461/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -36400,7 +36400,7 @@
           <t>C | 252呎 (1房)
 $615万
 $24,411/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -36408,7 +36408,7 @@
           <t>D | 198呎 (开放式)
 $521万
 $26,337/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -36416,7 +36416,7 @@
           <t>E | 308呎 (1房)
 $795万
 $25,807/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -36424,7 +36424,7 @@
           <t>F | 253呎 (1房)
 $608万
 $24,013/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -36432,7 +36432,7 @@
           <t>G | 194呎 (开放式)
 $475万
 $24,510/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -36440,7 +36440,7 @@
           <t>H | 249呎 (1房)
 $580万
 $23,275/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -36448,7 +36448,7 @@
           <t>J | 249呎 (1房)
 $588万
 $23,628/呎
-(18年-06月)</t>
+(18年-06月-24日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -36456,7 +36456,7 @@
           <t>K | 278呎 (1房)
 $660万
 $23,731/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -36464,7 +36464,7 @@
           <t>L | 193呎 (开放式)
 $498万
 $25,825/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -36479,7 +36479,7 @@
           <t>A | 417呎 (2房)
 $953万
 $22,852/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -36487,7 +36487,7 @@
           <t>B | 251呎 (1房)
 $652万
 $25,988/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -36495,7 +36495,7 @@
           <t>C | 252呎 (1房)
 $611万
 $24,244/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -36503,7 +36503,7 @@
           <t>D | 198呎 (开放式)
 $518万
 $26,148/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -36511,7 +36511,7 @@
           <t>E | 308呎 (1房)
 $794万
 $25,795/呎
-(18年-06月)</t>
+(18年-06月-15日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -36519,7 +36519,7 @@
           <t>F | 253呎 (1房)
 $610万
 $24,102/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -36527,7 +36527,7 @@
           <t>G | 194呎 (开放式)
 $482万
 $24,849/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -36535,7 +36535,7 @@
           <t>H | 249呎 (1房)
 $570万
 $22,872/呎
-(18年-06月)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -36543,7 +36543,7 @@
           <t>J | 248呎 (1房)
 $582万
 $23,474/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -36551,7 +36551,7 @@
           <t>K | 278呎 (1房)
 $650万
 $23,396/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -36559,7 +36559,7 @@
           <t>L | 193呎 (开放式)
 $505万
 $26,181/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -36574,7 +36574,7 @@
           <t>A | 417呎 (2房)
 $953万
 $22,847/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -36582,7 +36582,7 @@
           <t>B | 251呎 (1房)
 $626万
 $24,927/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -36590,7 +36590,7 @@
           <t>C | 252呎 (1房)
 $607万
 $24,072/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -36598,7 +36598,7 @@
           <t>D | 198呎 (开放式)
 $509万
 $25,688/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -36606,7 +36606,7 @@
           <t>E | 308呎 (1房)
 $741万
 $24,050/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -36614,7 +36614,7 @@
           <t>F | 253呎 (1房)
 $599万
 $23,690/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -36622,7 +36622,7 @@
           <t>G | 194呎 (开放式)
 $479万
 $24,682/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -36630,7 +36630,7 @@
           <t>H | 249呎 (1房)
 $566万
 $22,712/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -36638,7 +36638,7 @@
           <t>J | 248呎 (1房)
 $576万
 $23,225/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -36646,7 +36646,7 @@
           <t>K | 278呎 (1房)
 $641万
 $23,061/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -36654,7 +36654,7 @@
           <t>L | 193呎 (开放式)
 $486万
 $25,202/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -36669,7 +36669,7 @@
           <t>A | 417呎 (2房)
 $936万
 $22,445/呎
-(18年-06月)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -36677,7 +36677,7 @@
           <t>B | 251呎 (1房)
 $603万
 $24,030/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -36685,7 +36685,7 @@
           <t>C | 252呎 (1房)
 $594万
 $23,573/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -36693,7 +36693,7 @@
           <t>D | 198呎 (开放式)
 $508万
 $25,678/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -36701,7 +36701,7 @@
           <t>E | 307呎 (1房)
 $735万
 $23,950/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -36709,7 +36709,7 @@
           <t>F | 253呎 (1房)
 $595万
 $23,528/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -36717,7 +36717,7 @@
           <t>G | 194呎 (开放式)
 $461万
 $23,760/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -36725,7 +36725,7 @@
           <t>H | 249呎 (1房)
 $562万
 $22,552/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -36733,7 +36733,7 @@
           <t>J | 249呎 (1房)
 $590万
 $23,685/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -36741,7 +36741,7 @@
           <t>K | 278呎 (1房)
 $636万
 $22,895/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -36749,7 +36749,7 @@
           <t>L | 193呎 (开放式)
 $483万
 $25,030/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -36764,7 +36764,7 @@
           <t>A | 417呎 (2房)
 $929万
 $22,281/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -36772,7 +36772,7 @@
           <t>B | 251呎 (1房)
 $599万
 $23,856/呎
-(18年-06月)</t>
+(18年-06月-26日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -36780,7 +36780,7 @@
           <t>C | 252呎 (1房)
 $588万
 $23,324/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -36788,7 +36788,7 @@
           <t>D | 198呎 (开放式)
 $498万
 $25,127/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -36796,7 +36796,7 @@
           <t>E | 308呎 (1房)
 $722万
 $23,451/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -36804,7 +36804,7 @@
           <t>F | 253呎 (1房)
 $591万
 $23,367/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -36812,7 +36812,7 @@
           <t>G | 194呎 (开放式)
 $458万
 $23,593/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -36820,7 +36820,7 @@
           <t>H | 249呎 (1房)
 $558万
 $22,392/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -36828,7 +36828,7 @@
           <t>J | 249呎 (1房)
 $574万
 $23,036/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -36836,7 +36836,7 @@
           <t>K | 278呎 (1房)
 $625万
 $22,492/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -36844,7 +36844,7 @@
           <t>L | 193呎 (开放式)
 $490万
 $25,376/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -36859,7 +36859,7 @@
           <t>A | 417呎 (2房)
 $932万
 $22,352/呎
-(18年-06月)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -36867,7 +36867,7 @@
           <t>B | 251呎 (1房)
 $594万
 $23,682/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -36875,7 +36875,7 @@
           <t>C | 252呎 (1房)
 $590万
 $23,402/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -36883,7 +36883,7 @@
           <t>D | 198呎 (开放式)
 $494万
 $24,940/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -36891,7 +36891,7 @@
           <t>E | 308呎 (1房)
 $717万
 $23,275/呎
-(18年-10月)</t>
+(18年-10月-10日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -36899,7 +36899,7 @@
           <t>F | 253呎 (1房)
 $587万
 $23,202/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -36907,7 +36907,7 @@
           <t>G | 194呎 (开放式)
 $455万
 $23,432/呎
-(18年-06月)</t>
+(18年-06月-24日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -36915,7 +36915,7 @@
           <t>H | 248呎 (1房)
 $559万
 $22,556/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -36923,7 +36923,7 @@
           <t>J | 249呎 (1房)
 $564万
 $22,632/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -36931,7 +36931,7 @@
           <t>K | 278呎 (1房)
 $621万
 $22,325/呎
-(18年-06月)</t>
+(18年-06月-21日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -36939,7 +36939,7 @@
           <t>L | 193呎 (开放式)
 $469万
 $24,326/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -36954,7 +36954,7 @@
           <t>A | 417呎 (2房)
 $925万
 $22,186/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -36962,7 +36962,7 @@
           <t>B | 251呎 (1房)
 $596万
 $23,759/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -36970,7 +36970,7 @@
           <t>C | 252呎 (1房)
 $585万
 $23,230/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -36978,7 +36978,7 @@
           <t>D | 198呎 (开放式)
 $495万
 $25,013/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -36986,7 +36986,7 @@
           <t>E | 308呎 (1房)
 $719万
 $23,342/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -36994,7 +36994,7 @@
           <t>F | 253呎 (1房)
 $583万
 $23,040/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -37002,7 +37002,7 @@
           <t>G | 194呎 (开放式)
 $456万
 $23,510/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -37010,7 +37010,7 @@
           <t>H | 249呎 (1房)
 $550万
 $22,071/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -37018,7 +37018,7 @@
           <t>J | 249呎 (1房)
 $565万
 $22,701/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -37026,7 +37026,7 @@
           <t>K | 278呎 (1房)
 $636万
 $22,861/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -37034,7 +37034,7 @@
           <t>L | 193呎 (开放式)
 $459万
 $23,794/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -37049,7 +37049,7 @@
           <t>A | 417呎 (2房)
 $941万
 $22,566/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -37057,7 +37057,7 @@
           <t>B | 251呎 (1房)
 $594万
 $23,671/呎
-(18年-06月)</t>
+(18年-06月-25日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -37065,7 +37065,7 @@
           <t>C | 252呎 (1房)
 $595万
 $23,629/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -37073,7 +37073,7 @@
           <t>D | 198呎 (开放式)
 $488万
 $24,657/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -37081,7 +37081,7 @@
           <t>E | 308呎 (1房)
 $709万
 $23,010/呎
-(18年-06月)</t>
+(18年-06月-27日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -37089,7 +37089,7 @@
           <t>F | 253呎 (1房)
 $581万
 $22,961/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -37097,7 +37097,7 @@
           <t>G | 194呎 (开放式)
 $450万
 $23,182/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -37105,7 +37105,7 @@
           <t>H | 248呎 (1房)
 $548万
 $22,080/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -37113,7 +37113,7 @@
           <t>J | 249呎 (1房)
 $575万
 $23,087/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -37121,7 +37121,7 @@
           <t>K | 278呎 (1房)
 $620万
 $22,308/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -37129,7 +37129,7 @@
           <t>L | 193呎 (开放式)
 $458万
 $23,706/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -37144,7 +37144,7 @@
           <t>A | 417呎 (2房)
 $911万
 $21,857/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -37152,7 +37152,7 @@
           <t>B | 251呎 (1房)
 $584万
 $23,254/呎
-(18年-06月)</t>
+(18年-06月-24日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -37160,7 +37160,7 @@
           <t>C | 252呎 (1房)
 $573万
 $22,740/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -37168,7 +37168,7 @@
           <t>D | 198呎 (开放式)
 $490万
 $24,727/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -37176,7 +37176,7 @@
           <t>E | 308呎 (1房)
 $711万
 $23,077/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -37184,7 +37184,7 @@
           <t>F | 253呎 (1房)
 $577万
 $22,800/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -37192,7 +37192,7 @@
           <t>G | 194呎 (开放式)
 $446万
 $23,015/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -37200,7 +37200,7 @@
           <t>H | 249呎 (1房)
 $588万
 $23,609/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -37208,7 +37208,7 @@
           <t>J | 249呎 (1房)
 $553万
 $22,216/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -37216,7 +37216,7 @@
           <t>K | 278呎 (1房)
 $646万
 $23,248/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -37224,7 +37224,7 @@
           <t>L | 193呎 (开放式)
 $496万
 $25,716/呎
-(18年-07月)</t>
+(18年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -37239,7 +37239,7 @@
           <t>A | 417呎 (2房)
 $920万
 $22,061/呎
-(18年-07月)</t>
+(18年-07月-09日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -37247,7 +37247,7 @@
           <t>B | 251呎 (1房)
 $595万
 $23,719/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -37255,7 +37255,7 @@
           <t>C | 252呎 (1房)
 $567万
 $22,491/呎
-(18年-07月)</t>
+(18年-07月-08日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -37263,7 +37263,7 @@
           <t>D | 198呎 (开放式)
 $479万
 $24,196/呎
-(18年-06月)</t>
+(18年-06月-28日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -37271,7 +37271,7 @@
           <t>E | 308呎 (1房)
 $717万
 $23,285/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -37279,7 +37279,7 @@
           <t>F | 253呎 (1房)
 $578万
 $22,839/呎
-(18年-07月)</t>
+(18年-07月-03日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -37287,7 +37287,7 @@
           <t>G | 194呎 (开放式)
 $442万
 $22,771/呎
-(18年-06月)</t>
+(18年-06月-08日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -37295,7 +37295,7 @@
           <t>H | 249呎 (1房)
 $587万
 $23,591/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -37303,7 +37303,7 @@
           <t>J | 248呎 (1房)
 $548万
 $22,091/呎
-(18年-07月)</t>
+(18年-07月-02日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -37311,7 +37311,7 @@
           <t>K | 278呎 (1房)
 $646万
 $23,226/呎
-(18年-07月)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -37319,7 +37319,7 @@
           <t>L | 193呎 (开放式)
 $491万
 $25,428/呎
-(18年-07月)</t>
+(18年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -37334,7 +37334,7 @@
           <t>A | 379呎 (2房)
 $1170万
 $30,872/呎
-(19年-11月)</t>
+(19年-11月-03日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -37342,7 +37342,7 @@
           <t>B | 230呎 (1房)
 $700万
 $30,451/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -37350,7 +37350,7 @@
           <t>C | 230呎 (1房)
 $721万
 $31,359/呎
-(21年-08月)</t>
+(21年-08月-19日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -37358,7 +37358,7 @@
           <t>D | 175呎 (开放式)
 $398万
 $22,743/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -37366,7 +37366,7 @@
           <t>E | 286呎 (1房)
 $700万
 $24,476/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -37374,7 +37374,7 @@
           <t>F | 233呎 (1房)
 $628万
 $26,953/呎
-(23年-03月)</t>
+(23年-03月-15日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -37382,7 +37382,7 @@
           <t>G | 171呎 (开放式)
 $450万
 $26,316/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -37390,7 +37390,7 @@
           <t>H | 227呎 (1房)
 $693万
 $30,521/呎
-(21年-09月)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -37398,7 +37398,7 @@
           <t>J | 227呎 (1房)
 $716万
 $31,522/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -37406,7 +37406,7 @@
           <t>K | 257呎 (1房)
 $720万
 $28,016/呎
-(23年-04月)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -37414,7 +37414,7 @@
           <t>L | 171呎 (开放式)
 $380万
 $22,222/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
     </row>
